--- a/research/traditional_assets/database/data/philippines/philippines_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_business_consumer_services.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1113280538548104</v>
+        <v>0.1112747337201733</v>
       </c>
       <c r="C2">
-        <v>25032.76533773695</v>
+        <v>24802.68079630474</v>
       </c>
       <c r="D2">
-        <v>25016.46533773695</v>
+        <v>25036.83779630474</v>
       </c>
       <c r="E2">
-        <v>-92.3</v>
+        <v>158.157</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>250.457</v>
       </c>
       <c r="G2">
         <v>16.3</v>
@@ -1445,45 +1445,45 @@
         <v>29</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>18.9846406</v>
       </c>
       <c r="N2">
-        <v>29</v>
+        <v>10.0153594</v>
       </c>
       <c r="O2">
-        <v>7.25</v>
+        <v>2.503839849999999</v>
       </c>
       <c r="P2">
-        <v>21.75</v>
+        <v>7.511519549999998</v>
       </c>
       <c r="Q2">
-        <v>22.55</v>
+        <v>8.31151955</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1113280538548104</v>
+        <v>0.1118244785052256</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927493</v>
+        <v>0.9607366106313308</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.03772499999999999</v>
+        <v>0.05685</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>1.527550645335893</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1112747337201733</v>
+        <v>0.11404411855896</v>
       </c>
       <c r="C3">
-        <v>24802.68079630474</v>
+        <v>23536.21479115738</v>
       </c>
       <c r="D3">
-        <v>25036.83779630474</v>
+        <v>24020.82879115738</v>
       </c>
       <c r="E3">
-        <v>158.157</v>
+        <v>408.614</v>
       </c>
       <c r="F3">
-        <v>250.457</v>
+        <v>500.914</v>
       </c>
       <c r="G3">
         <v>16.3</v>
@@ -1527,45 +1527,45 @@
         <v>29</v>
       </c>
       <c r="M3">
-        <v>18.9846406</v>
+        <v>100.5835312</v>
       </c>
       <c r="N3">
-        <v>10.0153594</v>
+        <v>-71.58353120000001</v>
       </c>
       <c r="O3">
-        <v>2.503839849999999</v>
+        <v>-17.8958828</v>
       </c>
       <c r="P3">
-        <v>7.511519549999998</v>
+        <v>-53.68764840000001</v>
       </c>
       <c r="Q3">
-        <v>8.31151955</v>
+        <v>-52.8876484</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1118244785052256</v>
+        <v>0.1125689687818889</v>
       </c>
       <c r="T3">
-        <v>0.9607366106313308</v>
+        <v>0.9715698512905947</v>
       </c>
       <c r="U3">
-        <v>0.07580000000000001</v>
+        <v>0.2008</v>
       </c>
       <c r="V3">
-        <v>0.25</v>
+        <v>0.07207939424580471</v>
       </c>
       <c r="W3">
-        <v>0.05685</v>
+        <v>0.1863264576354424</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y3">
-        <v>1.527550645335893</v>
+        <v>0.2883175769832189</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.11404411855896</v>
+        <v>0.1166581399995858</v>
       </c>
       <c r="C4">
-        <v>23536.21479115738</v>
+        <v>22399.60749872726</v>
       </c>
       <c r="D4">
-        <v>24020.82879115738</v>
+        <v>23134.67849872726</v>
       </c>
       <c r="E4">
-        <v>408.614</v>
+        <v>659.071</v>
       </c>
       <c r="F4">
-        <v>500.914</v>
+        <v>751.371</v>
       </c>
       <c r="G4">
         <v>16.3</v>
@@ -1609,45 +1609,45 @@
         <v>29</v>
       </c>
       <c r="M4">
-        <v>100.5835312</v>
+        <v>177.1732818</v>
       </c>
       <c r="N4">
-        <v>-71.58353120000001</v>
+        <v>-148.1732818</v>
       </c>
       <c r="O4">
-        <v>-17.8958828</v>
+        <v>-37.04332045</v>
       </c>
       <c r="P4">
-        <v>-53.68764840000001</v>
+        <v>-111.12996135</v>
       </c>
       <c r="Q4">
-        <v>-52.8876484</v>
+        <v>-110.32996135</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1125689687818889</v>
+        <v>0.113271763759667</v>
       </c>
       <c r="T4">
-        <v>0.9715698512905947</v>
+        <v>0.9817963745469016</v>
       </c>
       <c r="U4">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>0.07207939424580471</v>
+        <v>0.04092039119185069</v>
       </c>
       <c r="W4">
-        <v>0.1863264576354424</v>
+        <v>0.2261509717569616</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y4">
-        <v>0.2883175769832189</v>
+        <v>0.1636815647674027</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1166581399995858</v>
+        <v>0.1185581399995858</v>
       </c>
       <c r="C5">
-        <v>22399.60749872726</v>
+        <v>21545.01343381834</v>
       </c>
       <c r="D5">
-        <v>23134.67849872726</v>
+        <v>22530.54143381834</v>
       </c>
       <c r="E5">
-        <v>659.071</v>
+        <v>909.5280000000001</v>
       </c>
       <c r="F5">
-        <v>751.371</v>
+        <v>1001.828</v>
       </c>
       <c r="G5">
         <v>16.3</v>
@@ -1691,37 +1691,37 @@
         <v>29</v>
       </c>
       <c r="M5">
-        <v>177.1732818</v>
+        <v>236.2310424</v>
       </c>
       <c r="N5">
-        <v>-148.1732818</v>
+        <v>-207.2310424</v>
       </c>
       <c r="O5">
-        <v>-37.04332045</v>
+        <v>-51.80776060000001</v>
       </c>
       <c r="P5">
-        <v>-111.12996135</v>
+        <v>-155.4232818</v>
       </c>
       <c r="Q5">
-        <v>-110.32996135</v>
+        <v>-154.6232818</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.113271763759667</v>
+        <v>0.1139745946321635</v>
       </c>
       <c r="T5">
-        <v>0.9817963745469016</v>
+        <v>0.9920234201150984</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>0.04092039119185069</v>
+        <v>0.03069029339388801</v>
       </c>
       <c r="W5">
-        <v>0.2261509717569616</v>
+        <v>0.2285632288177212</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>0.1636815647674027</v>
+        <v>0.1227611735755521</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1185581399995858</v>
+        <v>0.1204581399995859</v>
       </c>
       <c r="C6">
-        <v>21545.01343381834</v>
+        <v>20721.16914176294</v>
       </c>
       <c r="D6">
-        <v>22530.54143381834</v>
+        <v>21957.15414176294</v>
       </c>
       <c r="E6">
-        <v>909.5280000000001</v>
+        <v>1159.985</v>
       </c>
       <c r="F6">
-        <v>1001.828</v>
+        <v>1252.285</v>
       </c>
       <c r="G6">
         <v>16.3</v>
@@ -1773,37 +1773,37 @@
         <v>29</v>
       </c>
       <c r="M6">
-        <v>236.2310424</v>
+        <v>295.288803</v>
       </c>
       <c r="N6">
-        <v>-207.2310424</v>
+        <v>-266.288803</v>
       </c>
       <c r="O6">
-        <v>-51.80776060000001</v>
+        <v>-66.57220075000001</v>
       </c>
       <c r="P6">
-        <v>-155.4232818</v>
+        <v>-199.71660225</v>
       </c>
       <c r="Q6">
-        <v>-154.6232818</v>
+        <v>-198.91660225</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1139745946321635</v>
+        <v>0.114692221944081</v>
       </c>
       <c r="T6">
-        <v>0.9920234201150984</v>
+        <v>1.002465771905784</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>0.03069029339388801</v>
+        <v>0.02455223471511041</v>
       </c>
       <c r="W6">
-        <v>0.2285632288177212</v>
+        <v>0.230010583054177</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>0.1227611735755521</v>
+        <v>0.09820893886044169</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1204581399995859</v>
+        <v>0.1223581399995858</v>
       </c>
       <c r="C7">
-        <v>20721.16914176294</v>
+        <v>19925.78520297401</v>
       </c>
       <c r="D7">
-        <v>21957.15414176294</v>
+        <v>21412.22720297401</v>
       </c>
       <c r="E7">
-        <v>1159.985</v>
+        <v>1410.442</v>
       </c>
       <c r="F7">
-        <v>1252.285</v>
+        <v>1502.742</v>
       </c>
       <c r="G7">
         <v>16.3</v>
@@ -1855,37 +1855,37 @@
         <v>29</v>
       </c>
       <c r="M7">
-        <v>295.288803</v>
+        <v>354.3465636000001</v>
       </c>
       <c r="N7">
-        <v>-266.288803</v>
+        <v>-325.3465636000001</v>
       </c>
       <c r="O7">
-        <v>-66.57220075000001</v>
+        <v>-81.33664090000002</v>
       </c>
       <c r="P7">
-        <v>-199.71660225</v>
+        <v>-244.0099227000001</v>
       </c>
       <c r="Q7">
-        <v>-198.91660225</v>
+        <v>-243.2099227</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.114692221944081</v>
+        <v>0.1154251179222096</v>
       </c>
       <c r="T7">
-        <v>1.002465771905784</v>
+        <v>1.013130301394143</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.02455223471511041</v>
+        <v>0.02046019559592534</v>
       </c>
       <c r="W7">
-        <v>0.230010583054177</v>
+        <v>0.2309754858784808</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>0.09820893886044169</v>
+        <v>0.0818407823837014</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1223581399995858</v>
+        <v>0.1242581399995858</v>
       </c>
       <c r="C8">
-        <v>19925.78520297401</v>
+        <v>19156.79396693597</v>
       </c>
       <c r="D8">
-        <v>21412.22720297401</v>
+        <v>20893.69296693597</v>
       </c>
       <c r="E8">
-        <v>1410.442</v>
+        <v>1660.899</v>
       </c>
       <c r="F8">
-        <v>1502.742</v>
+        <v>1753.199</v>
       </c>
       <c r="G8">
         <v>16.3</v>
@@ -1937,37 +1937,37 @@
         <v>29</v>
       </c>
       <c r="M8">
-        <v>354.3465636</v>
+        <v>413.4043242</v>
       </c>
       <c r="N8">
-        <v>-325.3465636</v>
+        <v>-384.4043242</v>
       </c>
       <c r="O8">
-        <v>-81.33664090000001</v>
+        <v>-96.10108104999999</v>
       </c>
       <c r="P8">
-        <v>-244.0099227</v>
+        <v>-288.30324315</v>
       </c>
       <c r="Q8">
-        <v>-243.2099227</v>
+        <v>-287.5032431499999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1154251179222096</v>
+        <v>0.1161737751041688</v>
       </c>
       <c r="T8">
-        <v>1.013130301394143</v>
+        <v>1.024024175602682</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.02046019559592534</v>
+        <v>0.01753731051079315</v>
       </c>
       <c r="W8">
-        <v>0.2309754858784808</v>
+        <v>0.231664702181555</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.0818407823837014</v>
+        <v>0.07014924204317263</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1242581399995858</v>
+        <v>0.1261581399995858</v>
       </c>
       <c r="C9">
-        <v>19156.79396693596</v>
+        <v>18412.3233344977</v>
       </c>
       <c r="D9">
-        <v>20893.69296693596</v>
+        <v>20399.6793344977</v>
       </c>
       <c r="E9">
-        <v>1660.899</v>
+        <v>1911.356</v>
       </c>
       <c r="F9">
-        <v>1753.199</v>
+        <v>2003.656</v>
       </c>
       <c r="G9">
         <v>16.3</v>
@@ -2019,37 +2019,37 @@
         <v>29</v>
       </c>
       <c r="M9">
-        <v>413.4043242000001</v>
+        <v>472.4620848000001</v>
       </c>
       <c r="N9">
-        <v>-384.4043242000001</v>
+        <v>-443.4620848000001</v>
       </c>
       <c r="O9">
-        <v>-96.10108105000002</v>
+        <v>-110.8655212</v>
       </c>
       <c r="P9">
-        <v>-288.3032431500001</v>
+        <v>-332.5965636000001</v>
       </c>
       <c r="Q9">
-        <v>-287.5032431500001</v>
+        <v>-331.7965636000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1161737751041688</v>
+        <v>0.1169387074422576</v>
       </c>
       <c r="T9">
-        <v>1.024024175602682</v>
+        <v>1.035154873163581</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.01753731051079315</v>
+        <v>0.01534514669694401</v>
       </c>
       <c r="W9">
-        <v>0.231664702181555</v>
+        <v>0.2321816144088606</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.07014924204317263</v>
+        <v>0.06138058678777603</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1261581399995858</v>
+        <v>0.1280581399995858</v>
       </c>
       <c r="C10">
-        <v>18412.3233344977</v>
+        <v>17690.67417362777</v>
       </c>
       <c r="D10">
-        <v>20399.6793344977</v>
+        <v>19928.48717362777</v>
       </c>
       <c r="E10">
-        <v>1911.356</v>
+        <v>2161.813</v>
       </c>
       <c r="F10">
-        <v>2003.656</v>
+        <v>2254.113</v>
       </c>
       <c r="G10">
         <v>16.3</v>
@@ -2101,37 +2101,37 @@
         <v>29</v>
       </c>
       <c r="M10">
-        <v>472.4620848000001</v>
+        <v>531.5198454</v>
       </c>
       <c r="N10">
-        <v>-443.4620848000001</v>
+        <v>-502.5198454</v>
       </c>
       <c r="O10">
-        <v>-110.8655212</v>
+        <v>-125.62996135</v>
       </c>
       <c r="P10">
-        <v>-332.5965636000001</v>
+        <v>-376.88988405</v>
       </c>
       <c r="Q10">
-        <v>-331.7965636000001</v>
+        <v>-376.08988405</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1169387074422576</v>
+        <v>0.1177204514800846</v>
       </c>
       <c r="T10">
-        <v>1.035154873163581</v>
+        <v>1.046530201440104</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.01534514669694401</v>
+        <v>0.01364013039728356</v>
       </c>
       <c r="W10">
-        <v>0.2321816144088606</v>
+        <v>0.2325836572523206</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.06138058678777603</v>
+        <v>0.05456052158913427</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1280581399995858</v>
+        <v>0.1299581399995858</v>
       </c>
       <c r="C11">
-        <v>17690.67417362777</v>
+        <v>16990.30079441503</v>
       </c>
       <c r="D11">
-        <v>19928.48717362777</v>
+        <v>19478.57079441503</v>
       </c>
       <c r="E11">
-        <v>2161.813</v>
+        <v>2412.27</v>
       </c>
       <c r="F11">
-        <v>2254.113</v>
+        <v>2504.57</v>
       </c>
       <c r="G11">
         <v>16.3</v>
@@ -2183,37 +2183,37 @@
         <v>29</v>
       </c>
       <c r="M11">
-        <v>531.5198454</v>
+        <v>590.5776059999999</v>
       </c>
       <c r="N11">
-        <v>-502.5198454</v>
+        <v>-561.5776059999999</v>
       </c>
       <c r="O11">
-        <v>-125.62996135</v>
+        <v>-140.3944015</v>
       </c>
       <c r="P11">
-        <v>-376.88988405</v>
+        <v>-421.1832045</v>
       </c>
       <c r="Q11">
-        <v>-376.08988405</v>
+        <v>-420.3832045</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1177204514800846</v>
+        <v>0.1185195676076411</v>
       </c>
       <c r="T11">
-        <v>1.046530201440104</v>
+        <v>1.058158314789438</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.01364013039728356</v>
+        <v>0.01227611735755521</v>
       </c>
       <c r="W11">
-        <v>0.2325836572523206</v>
+        <v>0.2329052915270885</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.05456052158913427</v>
+        <v>0.04910446943022084</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1299581399995858</v>
+        <v>0.1318581399995858</v>
       </c>
       <c r="C12">
-        <v>16990.30079441503</v>
+        <v>16309.79401051816</v>
       </c>
       <c r="D12">
-        <v>19478.57079441503</v>
+        <v>19048.52101051816</v>
       </c>
       <c r="E12">
-        <v>2412.27</v>
+        <v>2662.727</v>
       </c>
       <c r="F12">
-        <v>2504.57</v>
+        <v>2755.027</v>
       </c>
       <c r="G12">
         <v>16.3</v>
@@ -2265,37 +2265,37 @@
         <v>29</v>
       </c>
       <c r="M12">
-        <v>590.5776060000001</v>
+        <v>649.6353666</v>
       </c>
       <c r="N12">
-        <v>-561.5776060000001</v>
+        <v>-620.6353666</v>
       </c>
       <c r="O12">
-        <v>-140.3944015</v>
+        <v>-155.15884165</v>
       </c>
       <c r="P12">
-        <v>-421.1832045</v>
+        <v>-465.47652495</v>
       </c>
       <c r="Q12">
-        <v>-420.3832045</v>
+        <v>-464.67652495</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1185195676076411</v>
+        <v>0.1193366414009854</v>
       </c>
       <c r="T12">
-        <v>1.058158314789438</v>
+        <v>1.070047734056735</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.01227611735755521</v>
+        <v>0.01116010668868655</v>
       </c>
       <c r="W12">
-        <v>0.2329052915270885</v>
+        <v>0.2331684468428077</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.04910446943022084</v>
+        <v>0.04464042675474622</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1318581399995858</v>
+        <v>0.1337581399995858</v>
       </c>
       <c r="C13">
-        <v>16309.79401051816</v>
+        <v>15647.8663959718</v>
       </c>
       <c r="D13">
-        <v>19048.52101051816</v>
+        <v>18637.0503959718</v>
       </c>
       <c r="E13">
-        <v>2662.727</v>
+        <v>2913.184</v>
       </c>
       <c r="F13">
-        <v>2755.027</v>
+        <v>3005.484</v>
       </c>
       <c r="G13">
         <v>16.3</v>
@@ -2347,37 +2347,37 @@
         <v>29</v>
       </c>
       <c r="M13">
-        <v>649.6353666</v>
+        <v>708.6931272</v>
       </c>
       <c r="N13">
-        <v>-620.6353666</v>
+        <v>-679.6931272</v>
       </c>
       <c r="O13">
-        <v>-155.15884165</v>
+        <v>-169.9232818</v>
       </c>
       <c r="P13">
-        <v>-465.47652495</v>
+        <v>-509.7698454</v>
       </c>
       <c r="Q13">
-        <v>-464.67652495</v>
+        <v>-508.9698454</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1193366414009854</v>
+        <v>0.1201722850532693</v>
       </c>
       <c r="T13">
-        <v>1.070047734056735</v>
+        <v>1.082207367398289</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.01116010668868655</v>
+        <v>0.01023009779796267</v>
       </c>
       <c r="W13">
-        <v>0.2331684468428077</v>
+        <v>0.2333877429392404</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.04464042675474622</v>
+        <v>0.04092039119185065</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1337581399995858</v>
+        <v>0.1356581399995858</v>
       </c>
       <c r="C14">
-        <v>15647.8663959718</v>
+        <v>15003.33941241204</v>
       </c>
       <c r="D14">
-        <v>18637.0503959718</v>
+        <v>18242.98041241205</v>
       </c>
       <c r="E14">
-        <v>2913.184</v>
+        <v>3163.641</v>
       </c>
       <c r="F14">
-        <v>3005.484</v>
+        <v>3255.941</v>
       </c>
       <c r="G14">
         <v>16.3</v>
@@ -2429,37 +2429,37 @@
         <v>29</v>
       </c>
       <c r="M14">
-        <v>708.6931272</v>
+        <v>767.7508878000001</v>
       </c>
       <c r="N14">
-        <v>-679.6931272</v>
+        <v>-738.7508878000001</v>
       </c>
       <c r="O14">
-        <v>-169.9232818</v>
+        <v>-184.68772195</v>
       </c>
       <c r="P14">
-        <v>-509.7698454</v>
+        <v>-554.0631658500001</v>
       </c>
       <c r="Q14">
-        <v>-508.9698454</v>
+        <v>-553.2631658500002</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1201722850532693</v>
+        <v>0.1210271389044563</v>
       </c>
       <c r="T14">
-        <v>1.082207367398289</v>
+        <v>1.094646532540798</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.01023009779796267</v>
+        <v>0.009443167198119388</v>
       </c>
       <c r="W14">
-        <v>0.2333877429392404</v>
+        <v>0.2335733011746834</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.04092039119185065</v>
+        <v>0.03777266879247754</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1356581399995858</v>
+        <v>0.1375581399995859</v>
       </c>
       <c r="C15">
-        <v>15003.33941241204</v>
+        <v>14375.13213561111</v>
       </c>
       <c r="D15">
-        <v>18242.98041241205</v>
+        <v>17865.23013561111</v>
       </c>
       <c r="E15">
-        <v>3163.641</v>
+        <v>3414.098</v>
       </c>
       <c r="F15">
-        <v>3255.941</v>
+        <v>3506.398000000001</v>
       </c>
       <c r="G15">
         <v>16.3</v>
@@ -2511,37 +2511,37 @@
         <v>29</v>
       </c>
       <c r="M15">
-        <v>767.7508878000001</v>
+        <v>826.8086484000002</v>
       </c>
       <c r="N15">
-        <v>-738.7508878000001</v>
+        <v>-797.8086484000002</v>
       </c>
       <c r="O15">
-        <v>-184.68772195</v>
+        <v>-199.4521621</v>
       </c>
       <c r="P15">
-        <v>-554.0631658500001</v>
+        <v>-598.3564863000001</v>
       </c>
       <c r="Q15">
-        <v>-553.2631658500002</v>
+        <v>-597.5564863000002</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1210271389044563</v>
+        <v>0.121901873077764</v>
       </c>
       <c r="T15">
-        <v>1.094646532540798</v>
+        <v>1.107374980593598</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.009443167198119388</v>
+        <v>0.008768655255396574</v>
       </c>
       <c r="W15">
-        <v>0.2335733011746834</v>
+        <v>0.2337323510907775</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.03777266879247754</v>
+        <v>0.03507462102158632</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1375581399995859</v>
+        <v>0.1394581399995858</v>
       </c>
       <c r="C16">
-        <v>14375.13213561111</v>
+        <v>13762.25135420982</v>
       </c>
       <c r="D16">
-        <v>17865.23013561111</v>
+        <v>17502.80635420982</v>
       </c>
       <c r="E16">
-        <v>3414.098</v>
+        <v>3664.555</v>
       </c>
       <c r="F16">
-        <v>3506.398000000001</v>
+        <v>3756.855</v>
       </c>
       <c r="G16">
         <v>16.3</v>
@@ -2593,37 +2593,37 @@
         <v>29</v>
       </c>
       <c r="M16">
-        <v>826.8086484000002</v>
+        <v>885.8664090000002</v>
       </c>
       <c r="N16">
-        <v>-797.8086484000002</v>
+        <v>-856.8664090000002</v>
       </c>
       <c r="O16">
-        <v>-199.4521621</v>
+        <v>-214.2166022500001</v>
       </c>
       <c r="P16">
-        <v>-598.3564863000001</v>
+        <v>-642.6498067500002</v>
       </c>
       <c r="Q16">
-        <v>-597.5564863000002</v>
+        <v>-641.8498067500002</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.121901873077764</v>
+        <v>0.12279718923162</v>
       </c>
       <c r="T16">
-        <v>1.107374980593598</v>
+        <v>1.120402921541758</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.008768655255396574</v>
+        <v>0.008184078238370135</v>
       </c>
       <c r="W16">
-        <v>0.2337323510907775</v>
+        <v>0.2338701943513923</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.03507462102158632</v>
+        <v>0.03273631295348056</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1394581399995858</v>
+        <v>0.1413581399995859</v>
       </c>
       <c r="C17">
-        <v>13762.25135420982</v>
+        <v>13163.78284966251</v>
       </c>
       <c r="D17">
-        <v>17502.80635420982</v>
+        <v>17154.79484966251</v>
       </c>
       <c r="E17">
-        <v>3664.555</v>
+        <v>3915.012</v>
       </c>
       <c r="F17">
-        <v>3756.855</v>
+        <v>4007.312</v>
       </c>
       <c r="G17">
         <v>16.3</v>
@@ -2675,37 +2675,37 @@
         <v>29</v>
       </c>
       <c r="M17">
-        <v>885.8664090000001</v>
+        <v>944.9241696000001</v>
       </c>
       <c r="N17">
-        <v>-856.8664090000001</v>
+        <v>-915.9241696000001</v>
       </c>
       <c r="O17">
-        <v>-214.21660225</v>
+        <v>-228.9810424</v>
       </c>
       <c r="P17">
-        <v>-642.64980675</v>
+        <v>-686.9431272000002</v>
       </c>
       <c r="Q17">
-        <v>-641.8498067500001</v>
+        <v>-686.1431272000002</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.12279718923162</v>
+        <v>0.1237138224367583</v>
       </c>
       <c r="T17">
-        <v>1.120402921541758</v>
+        <v>1.133741051560113</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.008184078238370137</v>
+        <v>0.007672573348472003</v>
       </c>
       <c r="W17">
-        <v>0.2338701943513923</v>
+        <v>0.2339908072044303</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.03273631295348056</v>
+        <v>0.03069029339388796</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1413581399995859</v>
+        <v>0.1432581399995858</v>
       </c>
       <c r="C18">
-        <v>13163.78284966251</v>
+        <v>12578.88369619542</v>
       </c>
       <c r="D18">
-        <v>17154.79484966251</v>
+        <v>16820.35269619542</v>
       </c>
       <c r="E18">
-        <v>3915.012</v>
+        <v>4165.469</v>
       </c>
       <c r="F18">
-        <v>4007.312</v>
+        <v>4257.769</v>
       </c>
       <c r="G18">
         <v>16.3</v>
@@ -2757,37 +2757,37 @@
         <v>29</v>
       </c>
       <c r="M18">
-        <v>944.9241696000001</v>
+        <v>1003.9819302</v>
       </c>
       <c r="N18">
-        <v>-915.9241696000001</v>
+        <v>-974.9819302000001</v>
       </c>
       <c r="O18">
-        <v>-228.9810424</v>
+        <v>-243.74548255</v>
       </c>
       <c r="P18">
-        <v>-686.9431272000002</v>
+        <v>-731.2364476500001</v>
       </c>
       <c r="Q18">
-        <v>-686.1431272000002</v>
+        <v>-730.4364476500001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1237138224367583</v>
+        <v>0.1246525431890084</v>
       </c>
       <c r="T18">
-        <v>1.133741051560113</v>
+        <v>1.147400582301801</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.007672573348472003</v>
+        <v>0.007221245504444238</v>
       </c>
       <c r="W18">
-        <v>0.2339908072044303</v>
+        <v>0.2340972303100521</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.03069029339388796</v>
+        <v>0.02888498201777701</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1432581399995858</v>
+        <v>0.1451581399995858</v>
       </c>
       <c r="C19">
-        <v>12578.88369619542</v>
+        <v>12006.77544424058</v>
       </c>
       <c r="D19">
-        <v>16820.35269619542</v>
+        <v>16498.70144424058</v>
       </c>
       <c r="E19">
-        <v>4165.469</v>
+        <v>4415.926</v>
       </c>
       <c r="F19">
-        <v>4257.769</v>
+        <v>4508.226000000001</v>
       </c>
       <c r="G19">
         <v>16.3</v>
@@ -2839,37 +2839,37 @@
         <v>29</v>
       </c>
       <c r="M19">
-        <v>1003.9819302</v>
+        <v>1063.0396908</v>
       </c>
       <c r="N19">
-        <v>-974.9819302000001</v>
+        <v>-1034.0396908</v>
       </c>
       <c r="O19">
-        <v>-243.74548255</v>
+        <v>-258.5099227000001</v>
       </c>
       <c r="P19">
-        <v>-731.2364476500001</v>
+        <v>-775.5297681000002</v>
       </c>
       <c r="Q19">
-        <v>-730.4364476500001</v>
+        <v>-774.7297681000002</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1246525431890084</v>
+        <v>0.1256141595693622</v>
       </c>
       <c r="T19">
-        <v>1.147400582301801</v>
+        <v>1.161393272329871</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.007221245504444238</v>
+        <v>0.00682006519864178</v>
       </c>
       <c r="W19">
-        <v>0.2340972303100521</v>
+        <v>0.2341918286261603</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.02888498201777701</v>
+        <v>0.02728026079456713</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1451581399995859</v>
+        <v>0.1470581399995858</v>
       </c>
       <c r="C20">
-        <v>12006.77544424057</v>
+        <v>11446.7380713028</v>
       </c>
       <c r="D20">
-        <v>16498.70144424057</v>
+        <v>16189.1210713028</v>
       </c>
       <c r="E20">
-        <v>4415.925999999999</v>
+        <v>4666.383</v>
       </c>
       <c r="F20">
-        <v>4508.226</v>
+        <v>4758.683</v>
       </c>
       <c r="G20">
         <v>16.3</v>
@@ -2921,37 +2921,37 @@
         <v>29</v>
       </c>
       <c r="M20">
-        <v>1063.0396908</v>
+        <v>1122.0974514</v>
       </c>
       <c r="N20">
-        <v>-1034.0396908</v>
+        <v>-1093.0974514</v>
       </c>
       <c r="O20">
-        <v>-258.5099227</v>
+        <v>-273.27436285</v>
       </c>
       <c r="P20">
-        <v>-775.5297681</v>
+        <v>-819.82308855</v>
       </c>
       <c r="Q20">
-        <v>-774.7297681</v>
+        <v>-819.02308855</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1256141595693622</v>
+        <v>0.1265995195640457</v>
       </c>
       <c r="T20">
-        <v>1.161393272329871</v>
+        <v>1.175731460877154</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.006820065198641781</v>
+        <v>0.006461114398713267</v>
       </c>
       <c r="W20">
-        <v>0.2341918286261603</v>
+        <v>0.2342764692247834</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.02728026079456713</v>
+        <v>0.0258444575948531</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1470581399995858</v>
+        <v>0.1489581399995858</v>
       </c>
       <c r="C21">
-        <v>11446.7380713028</v>
+        <v>10898.10460131605</v>
       </c>
       <c r="D21">
-        <v>16189.1210713028</v>
+        <v>15890.94460131605</v>
       </c>
       <c r="E21">
-        <v>4666.383</v>
+        <v>4916.84</v>
       </c>
       <c r="F21">
-        <v>4758.683</v>
+        <v>5009.14</v>
       </c>
       <c r="G21">
         <v>16.3</v>
@@ -3003,37 +3003,37 @@
         <v>29</v>
       </c>
       <c r="M21">
-        <v>1122.0974514</v>
+        <v>1181.155212</v>
       </c>
       <c r="N21">
-        <v>-1093.0974514</v>
+        <v>-1152.155212</v>
       </c>
       <c r="O21">
-        <v>-273.27436285</v>
+        <v>-288.038803</v>
       </c>
       <c r="P21">
-        <v>-819.82308855</v>
+        <v>-864.1164090000001</v>
       </c>
       <c r="Q21">
-        <v>-819.02308855</v>
+        <v>-863.3164090000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1265995195640457</v>
+        <v>0.1276095135585962</v>
       </c>
       <c r="T21">
-        <v>1.175731460877154</v>
+        <v>1.190428104138118</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.006461114398713267</v>
+        <v>0.006138058678777603</v>
       </c>
       <c r="W21">
-        <v>0.2342764692247834</v>
+        <v>0.2343526457635443</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.0258444575948531</v>
+        <v>0.02455223471511037</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1489581399995858</v>
+        <v>0.1508581399995858</v>
       </c>
       <c r="C22">
-        <v>10898.10460131605</v>
+        <v>10360.25630786064</v>
       </c>
       <c r="D22">
-        <v>15890.94460131605</v>
+        <v>15603.55330786064</v>
       </c>
       <c r="E22">
-        <v>4916.84</v>
+        <v>5167.297</v>
       </c>
       <c r="F22">
-        <v>5009.14</v>
+        <v>5259.597000000001</v>
       </c>
       <c r="G22">
         <v>16.3</v>
@@ -3085,37 +3085,37 @@
         <v>29</v>
       </c>
       <c r="M22">
-        <v>1181.155212</v>
+        <v>1240.2129726</v>
       </c>
       <c r="N22">
-        <v>-1152.155212</v>
+        <v>-1211.2129726</v>
       </c>
       <c r="O22">
-        <v>-288.038803</v>
+        <v>-302.8032431500001</v>
       </c>
       <c r="P22">
-        <v>-864.1164090000001</v>
+        <v>-908.4097294500002</v>
       </c>
       <c r="Q22">
-        <v>-863.3164090000001</v>
+        <v>-907.6097294500003</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1276095135585962</v>
+        <v>0.1286450770213633</v>
       </c>
       <c r="T22">
-        <v>1.190428104138118</v>
+        <v>1.205496814317082</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.006138058678777603</v>
+        <v>0.005845770170264383</v>
       </c>
       <c r="W22">
-        <v>0.2343526457635443</v>
+        <v>0.2344215673938517</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.02455223471511037</v>
+        <v>0.02338308068105754</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1508581399995858</v>
+        <v>0.1527581399995858</v>
       </c>
       <c r="C23">
-        <v>10360.25630786064</v>
+        <v>9832.618428639573</v>
       </c>
       <c r="D23">
-        <v>15603.55330786064</v>
+        <v>15326.37242863957</v>
       </c>
       <c r="E23">
-        <v>5167.297</v>
+        <v>5417.754</v>
       </c>
       <c r="F23">
-        <v>5259.597</v>
+        <v>5510.054</v>
       </c>
       <c r="G23">
         <v>16.3</v>
@@ -3167,37 +3167,37 @@
         <v>29</v>
       </c>
       <c r="M23">
-        <v>1240.2129726</v>
+        <v>1299.2707332</v>
       </c>
       <c r="N23">
-        <v>-1211.2129726</v>
+        <v>-1270.2707332</v>
       </c>
       <c r="O23">
-        <v>-302.80324315</v>
+        <v>-317.5676833</v>
       </c>
       <c r="P23">
-        <v>-908.40972945</v>
+        <v>-952.7030499</v>
       </c>
       <c r="Q23">
-        <v>-907.60972945</v>
+        <v>-951.9030499</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1286450770213633</v>
+        <v>0.129707193393432</v>
       </c>
       <c r="T23">
-        <v>1.205496814317082</v>
+        <v>1.220951901680121</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.005845770170264383</v>
+        <v>0.005580053344343276</v>
       </c>
       <c r="W23">
-        <v>0.2344215673938517</v>
+        <v>0.2344842234214038</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.02338308068105754</v>
+        <v>0.02232021337737311</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1527581399995858</v>
+        <v>0.1546581399995858</v>
       </c>
       <c r="C24">
-        <v>9832.618428639573</v>
+        <v>9314.656328749701</v>
       </c>
       <c r="D24">
-        <v>15326.37242863957</v>
+        <v>15058.8673287497</v>
       </c>
       <c r="E24">
-        <v>5417.754</v>
+        <v>5668.211</v>
       </c>
       <c r="F24">
-        <v>5510.054</v>
+        <v>5760.511</v>
       </c>
       <c r="G24">
         <v>16.3</v>
@@ -3249,37 +3249,37 @@
         <v>29</v>
       </c>
       <c r="M24">
-        <v>1299.2707332</v>
+        <v>1358.3284938</v>
       </c>
       <c r="N24">
-        <v>-1270.2707332</v>
+        <v>-1329.3284938</v>
       </c>
       <c r="O24">
-        <v>-317.5676833</v>
+        <v>-332.33212345</v>
       </c>
       <c r="P24">
-        <v>-952.7030499</v>
+        <v>-996.9963703500001</v>
       </c>
       <c r="Q24">
-        <v>-951.9030499</v>
+        <v>-996.1963703500002</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.129707193393432</v>
+        <v>0.1307968972037364</v>
       </c>
       <c r="T24">
-        <v>1.220951901680121</v>
+        <v>1.236808419883759</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.005580053344343276</v>
+        <v>0.005337442329371828</v>
       </c>
       <c r="W24">
-        <v>0.2344842234214038</v>
+        <v>0.2345414310987341</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.02232021337737311</v>
+        <v>0.02134976931748733</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1546581399995858</v>
+        <v>0.1565581399995858</v>
       </c>
       <c r="C25">
-        <v>9314.656328749701</v>
+        <v>8805.872058855752</v>
       </c>
       <c r="D25">
-        <v>15058.8673287497</v>
+        <v>14800.54005885575</v>
       </c>
       <c r="E25">
-        <v>5668.211</v>
+        <v>5918.668000000001</v>
       </c>
       <c r="F25">
-        <v>5760.511</v>
+        <v>6010.968000000001</v>
       </c>
       <c r="G25">
         <v>16.3</v>
@@ -3331,37 +3331,37 @@
         <v>29</v>
       </c>
       <c r="M25">
-        <v>1358.3284938</v>
+        <v>1417.3862544</v>
       </c>
       <c r="N25">
-        <v>-1329.3284938</v>
+        <v>-1388.3862544</v>
       </c>
       <c r="O25">
-        <v>-332.33212345</v>
+        <v>-347.0965636000001</v>
       </c>
       <c r="P25">
-        <v>-996.9963703500001</v>
+        <v>-1041.2896908</v>
       </c>
       <c r="Q25">
-        <v>-996.1963703500002</v>
+        <v>-1040.4896908</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1307968972037364</v>
+        <v>0.1319152774301013</v>
       </c>
       <c r="T25">
-        <v>1.236808419883759</v>
+        <v>1.25308221488223</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.005337442329371828</v>
+        <v>0.005115048898981335</v>
       </c>
       <c r="W25">
-        <v>0.2345414310987341</v>
+        <v>0.2345938714696202</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.02134976931748733</v>
+        <v>0.02046019559592538</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1565581399995858</v>
+        <v>0.1584581399995858</v>
       </c>
       <c r="C26">
-        <v>8805.872058855752</v>
+        <v>8305.801261646528</v>
       </c>
       <c r="D26">
-        <v>14800.54005885575</v>
+        <v>14550.92626164653</v>
       </c>
       <c r="E26">
-        <v>5918.668</v>
+        <v>6169.125</v>
       </c>
       <c r="F26">
-        <v>6010.968</v>
+        <v>6261.425</v>
       </c>
       <c r="G26">
         <v>16.3</v>
@@ -3413,37 +3413,37 @@
         <v>29</v>
       </c>
       <c r="M26">
-        <v>1417.3862544</v>
+        <v>1476.444015</v>
       </c>
       <c r="N26">
-        <v>-1388.3862544</v>
+        <v>-1447.444015</v>
       </c>
       <c r="O26">
-        <v>-347.0965636</v>
+        <v>-361.86100375</v>
       </c>
       <c r="P26">
-        <v>-1041.2896908</v>
+        <v>-1085.58301125</v>
       </c>
       <c r="Q26">
-        <v>-1040.4896908</v>
+        <v>-1084.78301125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1319152774301013</v>
+        <v>0.1330634811291693</v>
       </c>
       <c r="T26">
-        <v>1.25308221488223</v>
+        <v>1.269789977747326</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.005115048898981336</v>
+        <v>0.004910446943022083</v>
       </c>
       <c r="W26">
-        <v>0.2345938714696202</v>
+        <v>0.2346421166108354</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.02046019559592538</v>
+        <v>0.01964178777208836</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1584581399995858</v>
+        <v>0.1603581399995858</v>
       </c>
       <c r="C27">
-        <v>8305.801261646528</v>
+        <v>7814.010386138173</v>
       </c>
       <c r="D27">
-        <v>14550.92626164653</v>
+        <v>14309.59238613817</v>
       </c>
       <c r="E27">
-        <v>6169.125</v>
+        <v>6419.582</v>
       </c>
       <c r="F27">
-        <v>6261.425</v>
+        <v>6511.882000000001</v>
       </c>
       <c r="G27">
         <v>16.3</v>
@@ -3495,37 +3495,37 @@
         <v>29</v>
       </c>
       <c r="M27">
-        <v>1476.444015</v>
+        <v>1535.5017756</v>
       </c>
       <c r="N27">
-        <v>-1447.444015</v>
+        <v>-1506.5017756</v>
       </c>
       <c r="O27">
-        <v>-361.86100375</v>
+        <v>-376.6254439000001</v>
       </c>
       <c r="P27">
-        <v>-1085.58301125</v>
+        <v>-1129.8763317</v>
       </c>
       <c r="Q27">
-        <v>-1084.78301125</v>
+        <v>-1129.0763317</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1330634811291693</v>
+        <v>0.1342427173606446</v>
       </c>
       <c r="T27">
-        <v>1.269789977747326</v>
+        <v>1.286949301770938</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.004910446943022083</v>
+        <v>0.004721583599059694</v>
       </c>
       <c r="W27">
-        <v>0.2346421166108354</v>
+        <v>0.2346866505873417</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.01964178777208836</v>
+        <v>0.01888633439623877</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1603581399995858</v>
+        <v>0.1622581399995859</v>
       </c>
       <c r="C28">
-        <v>7814.010386138173</v>
+        <v>7330.094174667341</v>
       </c>
       <c r="D28">
-        <v>14309.59238613817</v>
+        <v>14076.13317466734</v>
       </c>
       <c r="E28">
-        <v>6419.582</v>
+        <v>6670.039000000001</v>
       </c>
       <c r="F28">
-        <v>6511.882000000001</v>
+        <v>6762.339000000001</v>
       </c>
       <c r="G28">
         <v>16.3</v>
@@ -3577,37 +3577,37 @@
         <v>29</v>
       </c>
       <c r="M28">
-        <v>1535.5017756</v>
+        <v>1594.5595362</v>
       </c>
       <c r="N28">
-        <v>-1506.5017756</v>
+        <v>-1565.5595362</v>
       </c>
       <c r="O28">
-        <v>-376.6254439000001</v>
+        <v>-391.3898840500001</v>
       </c>
       <c r="P28">
-        <v>-1129.8763317</v>
+        <v>-1174.16965215</v>
       </c>
       <c r="Q28">
-        <v>-1129.0763317</v>
+        <v>-1173.36965215</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1342427173606446</v>
+        <v>0.1354542614340781</v>
       </c>
       <c r="T28">
-        <v>1.286949301770938</v>
+        <v>1.304578744260951</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.004721583599059694</v>
+        <v>0.004546710132427853</v>
       </c>
       <c r="W28">
-        <v>0.2346866505873417</v>
+        <v>0.2347278857507735</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.01888633439623877</v>
+        <v>0.01818684052971142</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1622581399995859</v>
+        <v>0.1641581399995858</v>
       </c>
       <c r="C29">
-        <v>7330.094174667341</v>
+        <v>6853.67339193164</v>
       </c>
       <c r="D29">
-        <v>14076.13317466734</v>
+        <v>13850.16939193164</v>
       </c>
       <c r="E29">
-        <v>6670.039000000001</v>
+        <v>6920.496000000001</v>
       </c>
       <c r="F29">
-        <v>6762.339000000001</v>
+        <v>7012.796000000001</v>
       </c>
       <c r="G29">
         <v>16.3</v>
@@ -3659,37 +3659,37 @@
         <v>29</v>
       </c>
       <c r="M29">
-        <v>1594.5595362</v>
+        <v>1653.6172968</v>
       </c>
       <c r="N29">
-        <v>-1565.5595362</v>
+        <v>-1624.6172968</v>
       </c>
       <c r="O29">
-        <v>-391.3898840500001</v>
+        <v>-406.1543242000001</v>
       </c>
       <c r="P29">
-        <v>-1174.16965215</v>
+        <v>-1218.4629726</v>
       </c>
       <c r="Q29">
-        <v>-1173.36965215</v>
+        <v>-1217.6629726</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1354542614340781</v>
+        <v>0.1366994595095514</v>
       </c>
       <c r="T29">
-        <v>1.304578744260951</v>
+        <v>1.322697893486798</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.004546710132427853</v>
+        <v>0.004384327627698287</v>
       </c>
       <c r="W29">
-        <v>0.2347278857507735</v>
+        <v>0.2347661755453888</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.01818684052971142</v>
+        <v>0.0175373105107931</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1641581399995858</v>
+        <v>0.1660581399995859</v>
       </c>
       <c r="C30">
-        <v>6853.67339193164</v>
+        <v>6384.392769308167</v>
       </c>
       <c r="D30">
-        <v>13850.16939193164</v>
+        <v>13631.34576930817</v>
       </c>
       <c r="E30">
-        <v>6920.496000000001</v>
+        <v>7170.953000000001</v>
       </c>
       <c r="F30">
-        <v>7012.796000000001</v>
+        <v>7263.253000000002</v>
       </c>
       <c r="G30">
         <v>16.3</v>
@@ -3741,37 +3741,37 @@
         <v>29</v>
       </c>
       <c r="M30">
-        <v>1653.6172968</v>
+        <v>1712.6750574</v>
       </c>
       <c r="N30">
-        <v>-1624.6172968</v>
+        <v>-1683.6750574</v>
       </c>
       <c r="O30">
-        <v>-406.1543242000001</v>
+        <v>-420.9187643500001</v>
       </c>
       <c r="P30">
-        <v>-1218.4629726</v>
+        <v>-1262.75629305</v>
       </c>
       <c r="Q30">
-        <v>-1217.6629726</v>
+        <v>-1261.95629305</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1366994595095514</v>
+        <v>0.1379797335871507</v>
       </c>
       <c r="T30">
-        <v>1.322697893486798</v>
+        <v>1.341327441282387</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.004384327627698287</v>
+        <v>0.004233143916398346</v>
       </c>
       <c r="W30">
-        <v>0.2347661755453888</v>
+        <v>0.2348018246645133</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.0175373105107931</v>
+        <v>0.01693257566559336</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1660581399995858</v>
+        <v>0.1679581399995858</v>
       </c>
       <c r="C31">
-        <v>6384.392769308172</v>
+        <v>5921.919141011661</v>
       </c>
       <c r="D31">
-        <v>13631.34576930817</v>
+        <v>13419.32914101166</v>
       </c>
       <c r="E31">
-        <v>7170.953</v>
+        <v>7421.41</v>
       </c>
       <c r="F31">
-        <v>7263.253</v>
+        <v>7513.71</v>
       </c>
       <c r="G31">
         <v>16.3</v>
@@ -3823,37 +3823,37 @@
         <v>29</v>
       </c>
       <c r="M31">
-        <v>1712.6750574</v>
+        <v>1771.732818</v>
       </c>
       <c r="N31">
-        <v>-1683.6750574</v>
+        <v>-1742.732818</v>
       </c>
       <c r="O31">
-        <v>-420.91876435</v>
+        <v>-435.6832045</v>
       </c>
       <c r="P31">
-        <v>-1262.75629305</v>
+        <v>-1307.0496135</v>
       </c>
       <c r="Q31">
-        <v>-1261.95629305</v>
+        <v>-1306.2496135</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1379797335871507</v>
+        <v>0.13929658692411</v>
       </c>
       <c r="T31">
-        <v>1.341327441282387</v>
+        <v>1.360489261872135</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.004233143916398347</v>
+        <v>0.004092039119185069</v>
       </c>
       <c r="W31">
-        <v>0.2348018246645133</v>
+        <v>0.2348350971756962</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.01693257566559336</v>
+        <v>0.01636815647674028</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1679581399995858</v>
+        <v>0.1698581399995858</v>
       </c>
       <c r="C32">
-        <v>5921.919141011661</v>
+        <v>5465.93975152551</v>
       </c>
       <c r="D32">
-        <v>13419.32914101166</v>
+        <v>13213.80675152551</v>
       </c>
       <c r="E32">
-        <v>7421.41</v>
+        <v>7671.867</v>
       </c>
       <c r="F32">
-        <v>7513.71</v>
+        <v>7764.167</v>
       </c>
       <c r="G32">
         <v>16.3</v>
@@ -3905,37 +3905,37 @@
         <v>29</v>
       </c>
       <c r="M32">
-        <v>1771.732818</v>
+        <v>1830.7905786</v>
       </c>
       <c r="N32">
-        <v>-1742.732818</v>
+        <v>-1801.7905786</v>
       </c>
       <c r="O32">
-        <v>-435.6832045</v>
+        <v>-450.44764465</v>
       </c>
       <c r="P32">
-        <v>-1307.0496135</v>
+        <v>-1351.34293395</v>
       </c>
       <c r="Q32">
-        <v>-1306.2496135</v>
+        <v>-1350.54293395</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.13929658692411</v>
+        <v>0.1406516099230101</v>
       </c>
       <c r="T32">
-        <v>1.360489261872135</v>
+        <v>1.380206497551441</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.004092039119185069</v>
+        <v>0.003960037857275873</v>
       </c>
       <c r="W32">
-        <v>0.2348350971756962</v>
+        <v>0.2348662230732544</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.01636815647674028</v>
+        <v>0.01584015142910344</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1698581399995858</v>
+        <v>0.1717581399995858</v>
       </c>
       <c r="C33">
-        <v>5465.93975152551</v>
+        <v>5016.160716220914</v>
       </c>
       <c r="D33">
-        <v>13213.80675152551</v>
+        <v>13014.48471622092</v>
       </c>
       <c r="E33">
-        <v>7671.867</v>
+        <v>7922.324000000001</v>
       </c>
       <c r="F33">
-        <v>7764.167</v>
+        <v>8014.624000000001</v>
       </c>
       <c r="G33">
         <v>16.3</v>
@@ -3987,37 +3987,37 @@
         <v>29</v>
       </c>
       <c r="M33">
-        <v>1830.7905786</v>
+        <v>1889.8483392</v>
       </c>
       <c r="N33">
-        <v>-1801.7905786</v>
+        <v>-1860.8483392</v>
       </c>
       <c r="O33">
-        <v>-450.44764465</v>
+        <v>-465.2120848000001</v>
       </c>
       <c r="P33">
-        <v>-1351.34293395</v>
+        <v>-1395.6362544</v>
       </c>
       <c r="Q33">
-        <v>-1350.54293395</v>
+        <v>-1394.8362544</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1406516099230101</v>
+        <v>0.142046486539525</v>
       </c>
       <c r="T33">
-        <v>1.380206497551441</v>
+        <v>1.400503651927198</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.003960037857275873</v>
+        <v>0.003836286674236002</v>
       </c>
       <c r="W33">
-        <v>0.2348662230732544</v>
+        <v>0.2348954036022152</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.01584015142910344</v>
+        <v>0.01534514669694398</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1717581399995858</v>
+        <v>0.1736581399995858</v>
       </c>
       <c r="C34">
-        <v>5016.160716220914</v>
+        <v>4572.305619229202</v>
       </c>
       <c r="D34">
-        <v>13014.48471622092</v>
+        <v>12821.0866192292</v>
       </c>
       <c r="E34">
-        <v>7922.324000000001</v>
+        <v>8172.781</v>
       </c>
       <c r="F34">
-        <v>8014.624000000001</v>
+        <v>8265.081</v>
       </c>
       <c r="G34">
         <v>16.3</v>
@@ -4069,37 +4069,37 @@
         <v>29</v>
       </c>
       <c r="M34">
-        <v>1889.8483392</v>
+        <v>1948.9060998</v>
       </c>
       <c r="N34">
-        <v>-1860.8483392</v>
+        <v>-1919.9060998</v>
       </c>
       <c r="O34">
-        <v>-465.2120848000001</v>
+        <v>-479.9765249500001</v>
       </c>
       <c r="P34">
-        <v>-1395.6362544</v>
+        <v>-1439.92957485</v>
       </c>
       <c r="Q34">
-        <v>-1394.8362544</v>
+        <v>-1439.12957485</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.142046486539525</v>
+        <v>0.1434830012639955</v>
       </c>
       <c r="T34">
-        <v>1.400503651927198</v>
+        <v>1.421406691508201</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.003836286674236002</v>
+        <v>0.003720035562895517</v>
       </c>
       <c r="W34">
-        <v>0.2348954036022152</v>
+        <v>0.2349228156142693</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.01534514669694398</v>
+        <v>0.01488014225158207</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1736581399995858</v>
+        <v>0.1755581399995858</v>
       </c>
       <c r="C35">
-        <v>4572.305619229202</v>
+        <v>4134.114234499169</v>
       </c>
       <c r="D35">
-        <v>12821.0866192292</v>
+        <v>12633.35223449917</v>
       </c>
       <c r="E35">
-        <v>8172.781</v>
+        <v>8423.238000000001</v>
       </c>
       <c r="F35">
-        <v>8265.081</v>
+        <v>8515.538</v>
       </c>
       <c r="G35">
         <v>16.3</v>
@@ -4151,37 +4151,37 @@
         <v>29</v>
       </c>
       <c r="M35">
-        <v>1948.9060998</v>
+        <v>2007.9638604</v>
       </c>
       <c r="N35">
-        <v>-1919.9060998</v>
+        <v>-1978.9638604</v>
       </c>
       <c r="O35">
-        <v>-479.9765249500001</v>
+        <v>-494.7409651</v>
       </c>
       <c r="P35">
-        <v>-1439.92957485</v>
+        <v>-1484.2228953</v>
       </c>
       <c r="Q35">
-        <v>-1439.12957485</v>
+        <v>-1483.4228953</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1434830012639955</v>
+        <v>0.1449630467376924</v>
       </c>
       <c r="T35">
-        <v>1.421406691508201</v>
+        <v>1.442943156531052</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.003720035562895517</v>
+        <v>0.003610622752222119</v>
       </c>
       <c r="W35">
-        <v>0.2349228156142693</v>
+        <v>0.234948615155026</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.01488014225158207</v>
+        <v>0.0144424910088885</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1755581399995858</v>
+        <v>0.1774581399995858</v>
       </c>
       <c r="C36">
-        <v>4134.114234499169</v>
+        <v>3701.341357595364</v>
       </c>
       <c r="D36">
-        <v>12633.35223449917</v>
+        <v>12451.03635759537</v>
       </c>
       <c r="E36">
-        <v>8423.238000000001</v>
+        <v>8673.695000000002</v>
       </c>
       <c r="F36">
-        <v>8515.538</v>
+        <v>8765.995000000001</v>
       </c>
       <c r="G36">
         <v>16.3</v>
@@ -4233,37 +4233,37 @@
         <v>29</v>
       </c>
       <c r="M36">
-        <v>2007.9638604</v>
+        <v>2067.021621</v>
       </c>
       <c r="N36">
-        <v>-1978.9638604</v>
+        <v>-2038.021621</v>
       </c>
       <c r="O36">
-        <v>-494.7409651</v>
+        <v>-509.5054052500001</v>
       </c>
       <c r="P36">
-        <v>-1484.2228953</v>
+        <v>-1528.51621575</v>
       </c>
       <c r="Q36">
-        <v>-1483.4228953</v>
+        <v>-1527.71621575</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1449630467376924</v>
+        <v>0.1464886320721185</v>
       </c>
       <c r="T36">
-        <v>1.442943156531052</v>
+        <v>1.465142282016145</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.003610622752222119</v>
+        <v>0.00350746210215863</v>
       </c>
       <c r="W36">
-        <v>0.234948615155026</v>
+        <v>0.234972940436311</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.0144424910088885</v>
+        <v>0.01402984840863453</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1774581399995858</v>
+        <v>0.1793581399995858</v>
       </c>
       <c r="C37">
-        <v>3701.341357595364</v>
+        <v>3273.755737209483</v>
       </c>
       <c r="D37">
-        <v>12451.03635759537</v>
+        <v>12273.90773720949</v>
       </c>
       <c r="E37">
-        <v>8673.695000000002</v>
+        <v>8924.152000000002</v>
       </c>
       <c r="F37">
-        <v>8765.995000000001</v>
+        <v>9016.452000000001</v>
       </c>
       <c r="G37">
         <v>16.3</v>
@@ -4315,37 +4315,37 @@
         <v>29</v>
       </c>
       <c r="M37">
-        <v>2067.021621</v>
+        <v>2126.0793816</v>
       </c>
       <c r="N37">
-        <v>-2038.021621</v>
+        <v>-2097.0793816</v>
       </c>
       <c r="O37">
-        <v>-509.5054052500001</v>
+        <v>-524.2698454000001</v>
       </c>
       <c r="P37">
-        <v>-1528.51621575</v>
+        <v>-1572.8095362</v>
       </c>
       <c r="Q37">
-        <v>-1527.71621575</v>
+        <v>-1572.0095362</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1464886320721185</v>
+        <v>0.1480618919482453</v>
       </c>
       <c r="T37">
-        <v>1.465142282016145</v>
+        <v>1.488035130172648</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.00350746210215863</v>
+        <v>0.00341003259932089</v>
       </c>
       <c r="W37">
-        <v>0.234972940436311</v>
+        <v>0.2349959143130801</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.01402984840863453</v>
+        <v>0.01364013039728351</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1793581399995858</v>
+        <v>0.1812581399995858</v>
       </c>
       <c r="C38">
-        <v>3273.755737209485</v>
+        <v>2851.139096594536</v>
       </c>
       <c r="D38">
-        <v>12273.90773720949</v>
+        <v>12101.74809659454</v>
       </c>
       <c r="E38">
-        <v>8924.152</v>
+        <v>9174.609</v>
       </c>
       <c r="F38">
-        <v>9016.451999999999</v>
+        <v>9266.909</v>
       </c>
       <c r="G38">
         <v>16.3</v>
@@ -4397,37 +4397,37 @@
         <v>29</v>
       </c>
       <c r="M38">
-        <v>2126.0793816</v>
+        <v>2185.1371422</v>
       </c>
       <c r="N38">
-        <v>-2097.0793816</v>
+        <v>-2156.1371422</v>
       </c>
       <c r="O38">
-        <v>-524.2698454</v>
+        <v>-539.03428555</v>
       </c>
       <c r="P38">
-        <v>-1572.8095362</v>
+        <v>-1617.10285665</v>
       </c>
       <c r="Q38">
-        <v>-1572.0095362</v>
+        <v>-1616.30285665</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1480618919482453</v>
+        <v>0.1496850965823444</v>
       </c>
       <c r="T38">
-        <v>1.488035130172648</v>
+        <v>1.511654735413483</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.003410032599320891</v>
+        <v>0.003317869556096001</v>
       </c>
       <c r="W38">
-        <v>0.2349959143130801</v>
+        <v>0.2350176463586726</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.01364013039728351</v>
+        <v>0.01327147822438401</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1812581399995858</v>
+        <v>0.1831581399995859</v>
       </c>
       <c r="C39">
-        <v>2851.139096594536</v>
+        <v>2433.285236214806</v>
       </c>
       <c r="D39">
-        <v>12101.74809659454</v>
+        <v>11934.35123621481</v>
       </c>
       <c r="E39">
-        <v>9174.609</v>
+        <v>9425.066000000001</v>
       </c>
       <c r="F39">
-        <v>9266.909</v>
+        <v>9517.366</v>
       </c>
       <c r="G39">
         <v>16.3</v>
@@ -4479,37 +4479,37 @@
         <v>29</v>
       </c>
       <c r="M39">
-        <v>2185.1371422</v>
+        <v>2244.1949028</v>
       </c>
       <c r="N39">
-        <v>-2156.1371422</v>
+        <v>-2215.1949028</v>
       </c>
       <c r="O39">
-        <v>-539.03428555</v>
+        <v>-553.7987257</v>
       </c>
       <c r="P39">
-        <v>-1617.10285665</v>
+        <v>-1661.3961771</v>
       </c>
       <c r="Q39">
-        <v>-1616.30285665</v>
+        <v>-1660.5961771</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1496850965823444</v>
+        <v>0.1513606626562532</v>
       </c>
       <c r="T39">
-        <v>1.511654735413483</v>
+        <v>1.536036263404023</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.003317869556096001</v>
+        <v>0.003230557199356633</v>
       </c>
       <c r="W39">
-        <v>0.2350176463586726</v>
+        <v>0.2350382346123917</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.01327147822438401</v>
+        <v>0.01292222879742655</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1831581399995859</v>
+        <v>0.1850581399995859</v>
       </c>
       <c r="C40">
-        <v>2433.285236214806</v>
+        <v>2019.999209855014</v>
       </c>
       <c r="D40">
-        <v>11934.35123621481</v>
+        <v>11771.52220985501</v>
       </c>
       <c r="E40">
-        <v>9425.066000000001</v>
+        <v>9675.523000000001</v>
       </c>
       <c r="F40">
-        <v>9517.366</v>
+        <v>9767.823</v>
       </c>
       <c r="G40">
         <v>16.3</v>
@@ -4561,37 +4561,37 @@
         <v>29</v>
       </c>
       <c r="M40">
-        <v>2244.1949028</v>
+        <v>2303.2526634</v>
       </c>
       <c r="N40">
-        <v>-2215.1949028</v>
+        <v>-2274.2526634</v>
       </c>
       <c r="O40">
-        <v>-553.7987257</v>
+        <v>-568.56316585</v>
       </c>
       <c r="P40">
-        <v>-1661.3961771</v>
+        <v>-1705.68949755</v>
       </c>
       <c r="Q40">
-        <v>-1660.5961771</v>
+        <v>-1704.88949755</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1513606626562532</v>
+        <v>0.1530911653227492</v>
       </c>
       <c r="T40">
-        <v>1.536036263404023</v>
+        <v>1.561217185754909</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.003230557199356633</v>
+        <v>0.00314772239937313</v>
       </c>
       <c r="W40">
-        <v>0.2350382346123917</v>
+        <v>0.2350577670582278</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.01292222879742655</v>
+        <v>0.01259088959749255</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1850581399995859</v>
+        <v>0.1869581399995859</v>
       </c>
       <c r="C41">
-        <v>2019.999209855014</v>
+        <v>1611.096567267276</v>
       </c>
       <c r="D41">
-        <v>11771.52220985501</v>
+        <v>11613.07656726728</v>
       </c>
       <c r="E41">
-        <v>9675.523000000001</v>
+        <v>9925.980000000001</v>
       </c>
       <c r="F41">
-        <v>9767.823</v>
+        <v>10018.28</v>
       </c>
       <c r="G41">
         <v>16.3</v>
@@ -4643,37 +4643,37 @@
         <v>29</v>
       </c>
       <c r="M41">
-        <v>2303.2526634</v>
+        <v>2362.310424</v>
       </c>
       <c r="N41">
-        <v>-2274.2526634</v>
+        <v>-2333.310424</v>
       </c>
       <c r="O41">
-        <v>-568.56316585</v>
+        <v>-583.3276060000001</v>
       </c>
       <c r="P41">
-        <v>-1705.68949755</v>
+        <v>-1749.982818</v>
       </c>
       <c r="Q41">
-        <v>-1704.88949755</v>
+        <v>-1749.182818</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1530911653227492</v>
+        <v>0.1548793514114617</v>
       </c>
       <c r="T41">
-        <v>1.561217185754909</v>
+        <v>1.587237472184158</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.00314772239937313</v>
+        <v>0.003069029339388801</v>
       </c>
       <c r="W41">
-        <v>0.2350577670582278</v>
+        <v>0.2350763228817721</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.01259088959749255</v>
+        <v>0.01227611735755518</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1869581399995859</v>
+        <v>0.1888581399995858</v>
       </c>
       <c r="C42">
-        <v>1611.096567267276</v>
+        <v>1206.402657169941</v>
       </c>
       <c r="D42">
-        <v>11613.07656726728</v>
+        <v>11458.83965716994</v>
       </c>
       <c r="E42">
-        <v>9925.980000000001</v>
+        <v>10176.437</v>
       </c>
       <c r="F42">
-        <v>10018.28</v>
+        <v>10268.737</v>
       </c>
       <c r="G42">
         <v>16.3</v>
@@ -4725,37 +4725,37 @@
         <v>29</v>
       </c>
       <c r="M42">
-        <v>2362.310424</v>
+        <v>2421.3681846</v>
       </c>
       <c r="N42">
-        <v>-2333.310424</v>
+        <v>-2392.3681846</v>
       </c>
       <c r="O42">
-        <v>-583.3276060000001</v>
+        <v>-598.0920461500001</v>
       </c>
       <c r="P42">
-        <v>-1749.982818</v>
+        <v>-1794.27613845</v>
       </c>
       <c r="Q42">
-        <v>-1749.182818</v>
+        <v>-1793.47613845</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1548793514114617</v>
+        <v>0.1567281539777576</v>
       </c>
       <c r="T42">
-        <v>1.587237472184158</v>
+        <v>1.614139802221177</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.003069029339388801</v>
+        <v>0.002994174965257367</v>
       </c>
       <c r="W42">
-        <v>0.2350763228817721</v>
+        <v>0.2350939735431923</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.01227611735755518</v>
+        <v>0.01197669986102945</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1888581399995858</v>
+        <v>0.1907581399995859</v>
       </c>
       <c r="C43">
-        <v>1206.402657169941</v>
+        <v>805.7519850609788</v>
       </c>
       <c r="D43">
-        <v>11458.83965716994</v>
+        <v>11308.64598506098</v>
       </c>
       <c r="E43">
-        <v>10176.437</v>
+        <v>10426.894</v>
       </c>
       <c r="F43">
-        <v>10268.737</v>
+        <v>10519.194</v>
       </c>
       <c r="G43">
         <v>16.3</v>
@@ -4807,37 +4807,37 @@
         <v>29</v>
       </c>
       <c r="M43">
-        <v>2421.3681846</v>
+        <v>2480.425945200001</v>
       </c>
       <c r="N43">
-        <v>-2392.3681846</v>
+        <v>-2451.425945200001</v>
       </c>
       <c r="O43">
-        <v>-598.0920461500001</v>
+        <v>-612.8564863000001</v>
       </c>
       <c r="P43">
-        <v>-1794.27613845</v>
+        <v>-1838.5694589</v>
       </c>
       <c r="Q43">
-        <v>-1793.47613845</v>
+        <v>-1837.7694589</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1567281539777576</v>
+        <v>0.1586407083566845</v>
       </c>
       <c r="T43">
-        <v>1.614139802221177</v>
+        <v>1.641969798811197</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.002994174965257367</v>
+        <v>0.002922885085132191</v>
       </c>
       <c r="W43">
-        <v>0.2350939735431923</v>
+        <v>0.2351107836969258</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.01197669986102945</v>
+        <v>0.01169154034052877</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1907581399995859</v>
+        <v>0.1926581399995858</v>
       </c>
       <c r="C44">
-        <v>805.7519850609806</v>
+        <v>408.9876208816713</v>
       </c>
       <c r="D44">
-        <v>11308.64598506098</v>
+        <v>11162.33862088167</v>
       </c>
       <c r="E44">
-        <v>10426.894</v>
+        <v>10677.351</v>
       </c>
       <c r="F44">
-        <v>10519.194</v>
+        <v>10769.651</v>
       </c>
       <c r="G44">
         <v>16.3</v>
@@ -4889,37 +4889,37 @@
         <v>29</v>
       </c>
       <c r="M44">
-        <v>2480.4259452</v>
+        <v>2539.4837058</v>
       </c>
       <c r="N44">
-        <v>-2451.4259452</v>
+        <v>-2510.4837058</v>
       </c>
       <c r="O44">
-        <v>-612.8564863</v>
+        <v>-627.6209264500001</v>
       </c>
       <c r="P44">
-        <v>-1838.5694589</v>
+        <v>-1882.86277935</v>
       </c>
       <c r="Q44">
-        <v>-1837.7694589</v>
+        <v>-1882.06277935</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1586407083566845</v>
+        <v>0.1606203699068017</v>
       </c>
       <c r="T44">
-        <v>1.641969798811197</v>
+        <v>1.670776286509639</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.002922885085132192</v>
+        <v>0.002854911013384932</v>
       </c>
       <c r="W44">
-        <v>0.2351107836969258</v>
+        <v>0.2351268119830438</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.01169154034052877</v>
+        <v>0.01141964405353968</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1926581399995858</v>
+        <v>0.1945581399995858</v>
       </c>
       <c r="C45">
-        <v>408.9876208816713</v>
+        <v>15.96065207368338</v>
       </c>
       <c r="D45">
-        <v>11162.33862088167</v>
+        <v>11019.76865207368</v>
       </c>
       <c r="E45">
-        <v>10677.351</v>
+        <v>10927.808</v>
       </c>
       <c r="F45">
-        <v>10769.651</v>
+        <v>11020.108</v>
       </c>
       <c r="G45">
         <v>16.3</v>
@@ -4971,37 +4971,37 @@
         <v>29</v>
       </c>
       <c r="M45">
-        <v>2539.4837058</v>
+        <v>2598.5414664</v>
       </c>
       <c r="N45">
-        <v>-2510.4837058</v>
+        <v>-2569.5414664</v>
       </c>
       <c r="O45">
-        <v>-627.6209264500001</v>
+        <v>-642.3853666</v>
       </c>
       <c r="P45">
-        <v>-1882.86277935</v>
+        <v>-1927.1560998</v>
       </c>
       <c r="Q45">
-        <v>-1882.06277935</v>
+        <v>-1926.3560998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1606203699068017</v>
+        <v>0.1626707336551375</v>
       </c>
       <c r="T45">
-        <v>1.670776286509639</v>
+        <v>1.700611577340169</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.002854911013384932</v>
+        <v>0.002790026672171638</v>
       </c>
       <c r="W45">
-        <v>0.2351268119830438</v>
+        <v>0.2351421117107019</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.01141964405353968</v>
+        <v>0.0111601066886865</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1945581399995858</v>
+        <v>0.1964581399995858</v>
       </c>
       <c r="C46">
-        <v>15.96065207368338</v>
+        <v>-373.4703219777566</v>
       </c>
       <c r="D46">
-        <v>11019.76865207368</v>
+        <v>10880.79467802224</v>
       </c>
       <c r="E46">
-        <v>10927.808</v>
+        <v>11178.265</v>
       </c>
       <c r="F46">
-        <v>11020.108</v>
+        <v>11270.565</v>
       </c>
       <c r="G46">
         <v>16.3</v>
@@ -5053,37 +5053,37 @@
         <v>29</v>
       </c>
       <c r="M46">
-        <v>2598.5414664</v>
+        <v>2657.599227</v>
       </c>
       <c r="N46">
-        <v>-2569.5414664</v>
+        <v>-2628.599227</v>
       </c>
       <c r="O46">
-        <v>-642.3853666</v>
+        <v>-657.14980675</v>
       </c>
       <c r="P46">
-        <v>-1927.1560998</v>
+        <v>-1971.44942025</v>
       </c>
       <c r="Q46">
-        <v>-1926.3560998</v>
+        <v>-1970.64942025</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1626707336551375</v>
+        <v>0.1647956560852309</v>
       </c>
       <c r="T46">
-        <v>1.700611577340169</v>
+        <v>1.731531787837263</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.002790026672171638</v>
+        <v>0.002728026079456713</v>
       </c>
       <c r="W46">
-        <v>0.2351421117107019</v>
+        <v>0.2351567314504641</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.0111601066886865</v>
+        <v>0.01091210431782685</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1964581399995858</v>
+        <v>0.1983581399995859</v>
       </c>
       <c r="C47">
-        <v>-373.4703219777566</v>
+        <v>-759.4396577226653</v>
       </c>
       <c r="D47">
-        <v>10880.79467802224</v>
+        <v>10745.28234227734</v>
       </c>
       <c r="E47">
-        <v>11178.265</v>
+        <v>11428.722</v>
       </c>
       <c r="F47">
-        <v>11270.565</v>
+        <v>11521.022</v>
       </c>
       <c r="G47">
         <v>16.3</v>
@@ -5135,37 +5135,37 @@
         <v>29</v>
       </c>
       <c r="M47">
-        <v>2657.599227</v>
+        <v>2716.6569876</v>
       </c>
       <c r="N47">
-        <v>-2628.599227</v>
+        <v>-2687.6569876</v>
       </c>
       <c r="O47">
-        <v>-657.14980675</v>
+        <v>-671.9142469000001</v>
       </c>
       <c r="P47">
-        <v>-1971.44942025</v>
+        <v>-2015.7427407</v>
       </c>
       <c r="Q47">
-        <v>-1970.64942025</v>
+        <v>-2014.9427407</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1647956560852309</v>
+        <v>0.1669992793460685</v>
       </c>
       <c r="T47">
-        <v>1.731531787837263</v>
+        <v>1.763597191315731</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.002728026079456713</v>
+        <v>0.002668721164685914</v>
       </c>
       <c r="W47">
-        <v>0.2351567314504641</v>
+        <v>0.2351707155493671</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.01091210431782685</v>
+        <v>0.01067488465874367</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1983581399995859</v>
+        <v>0.2002581399995859</v>
       </c>
       <c r="C48">
-        <v>-759.4396577226653</v>
+        <v>-1142.07510070004</v>
       </c>
       <c r="D48">
-        <v>10745.28234227734</v>
+        <v>10613.10389929996</v>
       </c>
       <c r="E48">
-        <v>11428.722</v>
+        <v>11679.179</v>
       </c>
       <c r="F48">
-        <v>11521.022</v>
+        <v>11771.479</v>
       </c>
       <c r="G48">
         <v>16.3</v>
@@ -5217,37 +5217,37 @@
         <v>29</v>
       </c>
       <c r="M48">
-        <v>2716.6569876</v>
+        <v>2775.7147482</v>
       </c>
       <c r="N48">
-        <v>-2687.6569876</v>
+        <v>-2746.7147482</v>
       </c>
       <c r="O48">
-        <v>-671.9142469000001</v>
+        <v>-686.6786870500001</v>
       </c>
       <c r="P48">
-        <v>-2015.7427407</v>
+        <v>-2060.03606115</v>
       </c>
       <c r="Q48">
-        <v>-2014.9427407</v>
+        <v>-2059.23606115</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1669992793460685</v>
+        <v>0.1692860582016547</v>
       </c>
       <c r="T48">
-        <v>1.763597191315731</v>
+        <v>1.796872610019801</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.002668721164685914</v>
+        <v>0.002611939863309618</v>
       </c>
       <c r="W48">
-        <v>0.2351707155493671</v>
+        <v>0.2351841045802316</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.01067488465874367</v>
+        <v>0.0104477594532385</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2002581399995859</v>
+        <v>0.2021581399995859</v>
       </c>
       <c r="C49">
-        <v>-1142.07510070004</v>
+        <v>-1521.498187203268</v>
       </c>
       <c r="D49">
-        <v>10613.10389929996</v>
+        <v>10484.13781279673</v>
       </c>
       <c r="E49">
-        <v>11679.179</v>
+        <v>11929.636</v>
       </c>
       <c r="F49">
-        <v>11771.479</v>
+        <v>12021.936</v>
       </c>
       <c r="G49">
         <v>16.3</v>
@@ -5299,37 +5299,37 @@
         <v>29</v>
       </c>
       <c r="M49">
-        <v>2775.7147482</v>
+        <v>2834.772508800001</v>
       </c>
       <c r="N49">
-        <v>-2746.7147482</v>
+        <v>-2805.772508800001</v>
       </c>
       <c r="O49">
-        <v>-686.6786870500001</v>
+        <v>-701.4431272000002</v>
       </c>
       <c r="P49">
-        <v>-2060.03606115</v>
+        <v>-2104.3293816</v>
       </c>
       <c r="Q49">
-        <v>-2059.23606115</v>
+        <v>-2103.5293816</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1692860582016547</v>
+        <v>0.1716607900901481</v>
       </c>
       <c r="T49">
-        <v>1.796872610019801</v>
+        <v>1.831427852520182</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.002611939863309618</v>
+        <v>0.002557524449490668</v>
       </c>
       <c r="W49">
-        <v>0.2351841045802316</v>
+        <v>0.2351969357348101</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.0104477594532385</v>
+        <v>0.01023009779796269</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2021581399995858</v>
+        <v>0.2040581399995858</v>
       </c>
       <c r="C50">
-        <v>-1521.49818720326</v>
+        <v>-1897.824617011838</v>
       </c>
       <c r="D50">
-        <v>10484.13781279674</v>
+        <v>10358.26838298816</v>
       </c>
       <c r="E50">
-        <v>11929.636</v>
+        <v>12180.093</v>
       </c>
       <c r="F50">
-        <v>12021.936</v>
+        <v>12272.393</v>
       </c>
       <c r="G50">
         <v>16.3</v>
@@ -5381,37 +5381,37 @@
         <v>29</v>
       </c>
       <c r="M50">
-        <v>2834.7725088</v>
+        <v>2893.8302694</v>
       </c>
       <c r="N50">
-        <v>-2805.7725088</v>
+        <v>-2864.8302694</v>
       </c>
       <c r="O50">
-        <v>-701.4431272</v>
+        <v>-716.20756735</v>
       </c>
       <c r="P50">
-        <v>-2104.3293816</v>
+        <v>-2148.62270205</v>
       </c>
       <c r="Q50">
-        <v>-2103.5293816</v>
+        <v>-2147.82270205</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.171660790090148</v>
+        <v>0.1741286487193666</v>
       </c>
       <c r="T50">
-        <v>1.831427852520181</v>
+        <v>1.867338202569597</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.002557524449490668</v>
+        <v>0.00250533007297045</v>
       </c>
       <c r="W50">
-        <v>0.2351969357348101</v>
+        <v>0.2352092431687936</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.01023009779796269</v>
+        <v>0.01002132029188185</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2040581399995858</v>
+        <v>0.2059581399995858</v>
       </c>
       <c r="C51">
-        <v>-1897.824617011838</v>
+        <v>-2271.164599592235</v>
       </c>
       <c r="D51">
-        <v>10358.26838298816</v>
+        <v>10235.38540040777</v>
       </c>
       <c r="E51">
-        <v>12180.093</v>
+        <v>12430.55</v>
       </c>
       <c r="F51">
-        <v>12272.393</v>
+        <v>12522.85</v>
       </c>
       <c r="G51">
         <v>16.3</v>
@@ -5463,37 +5463,37 @@
         <v>29</v>
       </c>
       <c r="M51">
-        <v>2893.8302694</v>
+        <v>2952.88803</v>
       </c>
       <c r="N51">
-        <v>-2864.8302694</v>
+        <v>-2923.88803</v>
       </c>
       <c r="O51">
-        <v>-716.20756735</v>
+        <v>-730.9720075</v>
       </c>
       <c r="P51">
-        <v>-2148.62270205</v>
+        <v>-2192.9160225</v>
       </c>
       <c r="Q51">
-        <v>-2147.82270205</v>
+        <v>-2192.1160225</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1741286487193666</v>
+        <v>0.176695221693754</v>
       </c>
       <c r="T51">
-        <v>1.867338202569597</v>
+        <v>1.904684966620989</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.00250533007297045</v>
+        <v>0.002455223471511041</v>
       </c>
       <c r="W51">
-        <v>0.2352092431687936</v>
+        <v>0.2352210583054177</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.01002132029188185</v>
+        <v>0.009820893886044124</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2059581399995858</v>
+        <v>0.2078581399995859</v>
       </c>
       <c r="C52">
-        <v>-2271.164599592235</v>
+        <v>-2641.623175945169</v>
       </c>
       <c r="D52">
-        <v>10235.38540040777</v>
+        <v>10115.38382405483</v>
       </c>
       <c r="E52">
-        <v>12430.55</v>
+        <v>12681.007</v>
       </c>
       <c r="F52">
-        <v>12522.85</v>
+        <v>12773.307</v>
       </c>
       <c r="G52">
         <v>16.3</v>
@@ -5545,37 +5545,37 @@
         <v>29</v>
       </c>
       <c r="M52">
-        <v>2952.88803</v>
+        <v>3011.9457906</v>
       </c>
       <c r="N52">
-        <v>-2923.88803</v>
+        <v>-2982.9457906</v>
       </c>
       <c r="O52">
-        <v>-730.9720075</v>
+        <v>-745.7364476500001</v>
       </c>
       <c r="P52">
-        <v>-2192.9160225</v>
+        <v>-2237.20934295</v>
       </c>
       <c r="Q52">
-        <v>-2192.1160225</v>
+        <v>-2236.40934295</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.176695221693754</v>
+        <v>0.1793665527487286</v>
       </c>
       <c r="T52">
-        <v>1.904684966620989</v>
+        <v>1.943556088388764</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.002455223471511041</v>
+        <v>0.002407081834814746</v>
       </c>
       <c r="W52">
-        <v>0.2352210583054177</v>
+        <v>0.2352324101033507</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.009820893886044124</v>
+        <v>0.009628327339259002</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2078581399995859</v>
+        <v>0.2097581399995858</v>
       </c>
       <c r="C53">
-        <v>-2641.623175945169</v>
+        <v>-3009.300518074891</v>
       </c>
       <c r="D53">
-        <v>10115.38382405483</v>
+        <v>9998.16348192511</v>
       </c>
       <c r="E53">
-        <v>12681.007</v>
+        <v>12931.464</v>
       </c>
       <c r="F53">
-        <v>12773.307</v>
+        <v>13023.764</v>
       </c>
       <c r="G53">
         <v>16.3</v>
@@ -5627,37 +5627,37 @@
         <v>29</v>
       </c>
       <c r="M53">
-        <v>3011.9457906</v>
+        <v>3071.0035512</v>
       </c>
       <c r="N53">
-        <v>-2982.9457906</v>
+        <v>-3042.0035512</v>
       </c>
       <c r="O53">
-        <v>-745.7364476500001</v>
+        <v>-760.5008878000001</v>
       </c>
       <c r="P53">
-        <v>-2237.20934295</v>
+        <v>-2281.502663400001</v>
       </c>
       <c r="Q53">
-        <v>-2236.40934295</v>
+        <v>-2280.7026634</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1793665527487286</v>
+        <v>0.182149189264327</v>
       </c>
       <c r="T53">
-        <v>1.943556088388764</v>
+        <v>1.984046840230197</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.002407081834814746</v>
+        <v>0.002360791799529847</v>
       </c>
       <c r="W53">
-        <v>0.2352324101033507</v>
+        <v>0.2352433252936709</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.009628327339259002</v>
+        <v>0.00944316719811944</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2097581399995858</v>
+        <v>0.2116581399995859</v>
       </c>
       <c r="C54">
-        <v>-3009.300518074891</v>
+        <v>-3374.292207874894</v>
       </c>
       <c r="D54">
-        <v>9998.16348192511</v>
+        <v>9883.628792125108</v>
       </c>
       <c r="E54">
-        <v>12931.464</v>
+        <v>13181.921</v>
       </c>
       <c r="F54">
-        <v>13023.764</v>
+        <v>13274.221</v>
       </c>
       <c r="G54">
         <v>16.3</v>
@@ -5709,37 +5709,37 @@
         <v>29</v>
       </c>
       <c r="M54">
-        <v>3071.0035512</v>
+        <v>3130.061311800001</v>
       </c>
       <c r="N54">
-        <v>-3042.0035512</v>
+        <v>-3101.061311800001</v>
       </c>
       <c r="O54">
-        <v>-760.5008878000001</v>
+        <v>-775.2653279500001</v>
       </c>
       <c r="P54">
-        <v>-2281.502663400001</v>
+        <v>-2325.795983850001</v>
       </c>
       <c r="Q54">
-        <v>-2280.7026634</v>
+        <v>-2324.99598385</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.182149189264327</v>
+        <v>0.1850502358444192</v>
       </c>
       <c r="T54">
-        <v>1.984046840230197</v>
+        <v>2.026260602788287</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.002360791799529847</v>
+        <v>0.002316248558029284</v>
       </c>
       <c r="W54">
-        <v>0.2352433252936709</v>
+        <v>0.2352538285900167</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.00944316719811944</v>
+        <v>0.00926499423211713</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2116581399995859</v>
+        <v>0.2135581399995858</v>
       </c>
       <c r="C55">
-        <v>-3374.292207874894</v>
+        <v>-3736.689497061956</v>
       </c>
       <c r="D55">
-        <v>9883.628792125108</v>
+        <v>9771.688502938046</v>
       </c>
       <c r="E55">
-        <v>13181.921</v>
+        <v>13432.378</v>
       </c>
       <c r="F55">
-        <v>13274.221</v>
+        <v>13524.678</v>
       </c>
       <c r="G55">
         <v>16.3</v>
@@ -5791,37 +5791,37 @@
         <v>29</v>
       </c>
       <c r="M55">
-        <v>3130.061311800001</v>
+        <v>3189.119072400001</v>
       </c>
       <c r="N55">
-        <v>-3101.061311800001</v>
+        <v>-3160.119072400001</v>
       </c>
       <c r="O55">
-        <v>-775.2653279500001</v>
+        <v>-790.0297681000002</v>
       </c>
       <c r="P55">
-        <v>-2325.795983850001</v>
+        <v>-2370.089304300001</v>
       </c>
       <c r="Q55">
-        <v>-2324.99598385</v>
+        <v>-2369.2893043</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1850502358444192</v>
+        <v>0.1880774148845152</v>
       </c>
       <c r="T55">
-        <v>2.026260602788287</v>
+        <v>2.070309746327162</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.002316248558029284</v>
+        <v>0.002273355066213927</v>
       </c>
       <c r="W55">
-        <v>0.2352538285900167</v>
+        <v>0.2352639428753868</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.00926499423211713</v>
+        <v>0.009093420264855712</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2135581399995858</v>
+        <v>0.2154581399995859</v>
       </c>
       <c r="C56">
-        <v>-3736.689497061956</v>
+        <v>-4096.579549644215</v>
       </c>
       <c r="D56">
-        <v>9771.688502938046</v>
+        <v>9662.255450355788</v>
       </c>
       <c r="E56">
-        <v>13432.378</v>
+        <v>13682.835</v>
       </c>
       <c r="F56">
-        <v>13524.678</v>
+        <v>13775.135</v>
       </c>
       <c r="G56">
         <v>16.3</v>
@@ -5873,37 +5873,37 @@
         <v>29</v>
       </c>
       <c r="M56">
-        <v>3189.119072400001</v>
+        <v>3248.176833</v>
       </c>
       <c r="N56">
-        <v>-3160.119072400001</v>
+        <v>-3219.176833</v>
       </c>
       <c r="O56">
-        <v>-790.0297681000002</v>
+        <v>-804.7942082500001</v>
       </c>
       <c r="P56">
-        <v>-2370.089304300001</v>
+        <v>-2414.38262475</v>
       </c>
       <c r="Q56">
-        <v>-2369.2893043</v>
+        <v>-2413.58262475</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1880774148845152</v>
+        <v>0.1912391352152822</v>
       </c>
       <c r="T56">
-        <v>2.070309746327162</v>
+        <v>2.116316629578877</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.002273355066213927</v>
+        <v>0.00223202133773731</v>
       </c>
       <c r="W56">
-        <v>0.2352639428753868</v>
+        <v>0.2352736893685616</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.009093420264855712</v>
+        <v>0.008928085350949244</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2154581399995859</v>
+        <v>0.2173581399995858</v>
       </c>
       <c r="C57">
-        <v>-4096.579549644215</v>
+        <v>-4454.045668277233</v>
       </c>
       <c r="D57">
-        <v>9662.255450355788</v>
+        <v>9555.24633172277</v>
       </c>
       <c r="E57">
-        <v>13682.835</v>
+        <v>13933.292</v>
       </c>
       <c r="F57">
-        <v>13775.135</v>
+        <v>14025.592</v>
       </c>
       <c r="G57">
         <v>16.3</v>
@@ -5955,37 +5955,37 @@
         <v>29</v>
       </c>
       <c r="M57">
-        <v>3248.176833</v>
+        <v>3307.234593600001</v>
       </c>
       <c r="N57">
-        <v>-3219.176833</v>
+        <v>-3278.234593600001</v>
       </c>
       <c r="O57">
-        <v>-804.7942082500001</v>
+        <v>-819.5586484000002</v>
       </c>
       <c r="P57">
-        <v>-2414.38262475</v>
+        <v>-2458.675945200001</v>
       </c>
       <c r="Q57">
-        <v>-2413.58262475</v>
+        <v>-2457.8759452</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1912391352152822</v>
+        <v>0.1945445701065386</v>
       </c>
       <c r="T57">
-        <v>2.116316629578877</v>
+        <v>2.164414734796579</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.00223202133773731</v>
+        <v>0.002192163813849143</v>
       </c>
       <c r="W57">
-        <v>0.2352736893685616</v>
+        <v>0.2352830877726944</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.008928085350949244</v>
+        <v>0.008768655255396607</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2173581399995858</v>
+        <v>0.2192581399995858</v>
       </c>
       <c r="C58">
-        <v>-4454.045668277233</v>
+        <v>-4809.16750574359</v>
       </c>
       <c r="D58">
-        <v>9555.24633172277</v>
+        <v>9450.581494256414</v>
       </c>
       <c r="E58">
-        <v>13933.292</v>
+        <v>14183.749</v>
       </c>
       <c r="F58">
-        <v>14025.592</v>
+        <v>14276.049</v>
       </c>
       <c r="G58">
         <v>16.3</v>
@@ -6037,37 +6037,37 @@
         <v>29</v>
       </c>
       <c r="M58">
-        <v>3307.234593600001</v>
+        <v>3366.292354200001</v>
       </c>
       <c r="N58">
-        <v>-3278.234593600001</v>
+        <v>-3337.292354200001</v>
       </c>
       <c r="O58">
-        <v>-819.5586484000002</v>
+        <v>-834.3230885500002</v>
       </c>
       <c r="P58">
-        <v>-2458.675945200001</v>
+        <v>-2502.969265650001</v>
       </c>
       <c r="Q58">
-        <v>-2457.8759452</v>
+        <v>-2502.16926565</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1945445701065386</v>
+        <v>0.1980037461555279</v>
       </c>
       <c r="T58">
-        <v>2.164414734796579</v>
+        <v>2.214749961187197</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.002192163813849143</v>
+        <v>0.002153704799571088</v>
       </c>
       <c r="W58">
-        <v>0.2352830877726944</v>
+        <v>0.2352921564082611</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.008768655255396607</v>
+        <v>0.008614819198284329</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2192581399995858</v>
+        <v>0.2211581399995858</v>
       </c>
       <c r="C59">
-        <v>-4809.16750574359</v>
+        <v>-5162.021262684157</v>
       </c>
       <c r="D59">
-        <v>9450.581494256414</v>
+        <v>9348.184737315847</v>
       </c>
       <c r="E59">
-        <v>14183.749</v>
+        <v>14434.206</v>
       </c>
       <c r="F59">
-        <v>14276.049</v>
+        <v>14526.506</v>
       </c>
       <c r="G59">
         <v>16.3</v>
@@ -6119,37 +6119,37 @@
         <v>29</v>
       </c>
       <c r="M59">
-        <v>3366.292354200001</v>
+        <v>3425.350114800001</v>
       </c>
       <c r="N59">
-        <v>-3337.292354200001</v>
+        <v>-3396.350114800001</v>
       </c>
       <c r="O59">
-        <v>-834.3230885500002</v>
+        <v>-849.0875287000002</v>
       </c>
       <c r="P59">
-        <v>-2502.969265650001</v>
+        <v>-2547.262586100001</v>
       </c>
       <c r="Q59">
-        <v>-2502.16926565</v>
+        <v>-2546.4625861</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1980037461555279</v>
+        <v>0.2016276448735167</v>
       </c>
       <c r="T59">
-        <v>2.214749961187197</v>
+        <v>2.267482103120225</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.002153704799571088</v>
+        <v>0.002116571958199173</v>
       </c>
       <c r="W59">
-        <v>0.2352921564082611</v>
+        <v>0.2353009123322566</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.008614819198284329</v>
+        <v>0.008466287832796682</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2211581399995858</v>
+        <v>0.2230581399995858</v>
       </c>
       <c r="C60">
-        <v>-5162.021262684153</v>
+        <v>-5512.679872612709</v>
       </c>
       <c r="D60">
-        <v>9348.184737315847</v>
+        <v>9247.983127387291</v>
       </c>
       <c r="E60">
-        <v>14434.206</v>
+        <v>14684.663</v>
       </c>
       <c r="F60">
-        <v>14526.506</v>
+        <v>14776.963</v>
       </c>
       <c r="G60">
         <v>16.3</v>
@@ -6201,37 +6201,37 @@
         <v>29</v>
       </c>
       <c r="M60">
-        <v>3425.3501148</v>
+        <v>3484.4078754</v>
       </c>
       <c r="N60">
-        <v>-3396.3501148</v>
+        <v>-3455.4078754</v>
       </c>
       <c r="O60">
-        <v>-849.0875287</v>
+        <v>-863.85196885</v>
       </c>
       <c r="P60">
-        <v>-2547.2625861</v>
+        <v>-2591.55590655</v>
       </c>
       <c r="Q60">
-        <v>-2546.4625861</v>
+        <v>-2590.75590655</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2016276448735166</v>
+        <v>0.2054283191387243</v>
       </c>
       <c r="T60">
-        <v>2.267482103120225</v>
+        <v>2.322786544659742</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.002116571958199173</v>
+        <v>0.002080697857212747</v>
       </c>
       <c r="W60">
-        <v>0.2353009123322566</v>
+        <v>0.2353093714452692</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.008466287832796682</v>
+        <v>0.008322791428850951</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2230581399995858</v>
+        <v>0.2249581399995859</v>
       </c>
       <c r="C61">
-        <v>-5512.679872612709</v>
+        <v>-5861.213175157918</v>
       </c>
       <c r="D61">
-        <v>9247.983127387291</v>
+        <v>9149.906824842083</v>
       </c>
       <c r="E61">
-        <v>14684.663</v>
+        <v>14935.12</v>
       </c>
       <c r="F61">
-        <v>14776.963</v>
+        <v>15027.42</v>
       </c>
       <c r="G61">
         <v>16.3</v>
@@ -6283,37 +6283,37 @@
         <v>29</v>
       </c>
       <c r="M61">
-        <v>3484.4078754</v>
+        <v>3543.465636</v>
       </c>
       <c r="N61">
-        <v>-3455.4078754</v>
+        <v>-3514.465636</v>
       </c>
       <c r="O61">
-        <v>-863.85196885</v>
+        <v>-878.6164090000001</v>
       </c>
       <c r="P61">
-        <v>-2591.55590655</v>
+        <v>-2635.849227</v>
       </c>
       <c r="Q61">
-        <v>-2590.75590655</v>
+        <v>-2635.049227</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2054283191387243</v>
+        <v>0.2094190271171925</v>
       </c>
       <c r="T61">
-        <v>2.322786544659742</v>
+        <v>2.380856208276236</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.002080697857212747</v>
+        <v>0.002046019559592534</v>
       </c>
       <c r="W61">
-        <v>0.2353093714452692</v>
+        <v>0.2353175485878481</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.008322791428850951</v>
+        <v>0.008184078238370085</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2249581399995859</v>
+        <v>0.2268581399995859</v>
       </c>
       <c r="C62">
-        <v>-5861.213175157918</v>
+        <v>-6207.688078397397</v>
       </c>
       <c r="D62">
-        <v>9149.906824842083</v>
+        <v>9053.888921602604</v>
       </c>
       <c r="E62">
-        <v>14935.12</v>
+        <v>15185.577</v>
       </c>
       <c r="F62">
-        <v>15027.42</v>
+        <v>15277.877</v>
       </c>
       <c r="G62">
         <v>16.3</v>
@@ -6365,37 +6365,37 @@
         <v>29</v>
       </c>
       <c r="M62">
-        <v>3543.465636</v>
+        <v>3602.5233966</v>
       </c>
       <c r="N62">
-        <v>-3514.465636</v>
+        <v>-3573.5233966</v>
       </c>
       <c r="O62">
-        <v>-878.6164090000001</v>
+        <v>-893.38084915</v>
       </c>
       <c r="P62">
-        <v>-2635.849227</v>
+        <v>-2680.14254745</v>
       </c>
       <c r="Q62">
-        <v>-2635.049227</v>
+        <v>-2679.34254745</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2094190271171925</v>
+        <v>0.2136143867868641</v>
       </c>
       <c r="T62">
-        <v>2.380856208276236</v>
+        <v>2.441903803360243</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.002046019559592534</v>
+        <v>0.002012478255336919</v>
       </c>
       <c r="W62">
-        <v>0.2353175485878481</v>
+        <v>0.2353254576273916</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.008184078238370085</v>
+        <v>0.008049913021347721</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2268581399995859</v>
+        <v>0.2287581399995858</v>
       </c>
       <c r="C63">
-        <v>-6207.688078397397</v>
+        <v>-6552.168711076891</v>
       </c>
       <c r="D63">
-        <v>9053.888921602604</v>
+        <v>8959.865288923111</v>
       </c>
       <c r="E63">
-        <v>15185.577</v>
+        <v>15436.034</v>
       </c>
       <c r="F63">
-        <v>15277.877</v>
+        <v>15528.334</v>
       </c>
       <c r="G63">
         <v>16.3</v>
@@ -6447,37 +6447,37 @@
         <v>29</v>
       </c>
       <c r="M63">
-        <v>3602.5233966</v>
+        <v>3661.5811572</v>
       </c>
       <c r="N63">
-        <v>-3573.5233966</v>
+        <v>-3632.5811572</v>
       </c>
       <c r="O63">
-        <v>-893.38084915</v>
+        <v>-908.1452893000001</v>
       </c>
       <c r="P63">
-        <v>-2680.14254745</v>
+        <v>-2724.4358679</v>
       </c>
       <c r="Q63">
-        <v>-2679.34254745</v>
+        <v>-2723.6358679</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2136143867868641</v>
+        <v>0.2180305548602026</v>
       </c>
       <c r="T63">
-        <v>2.441903803360243</v>
+        <v>2.506164429764459</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.002012478255336919</v>
+        <v>0.001980018928637937</v>
       </c>
       <c r="W63">
-        <v>0.2353254576273916</v>
+        <v>0.2353331115366272</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.008049913021347721</v>
+        <v>0.007920075714551778</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2287581399995858</v>
+        <v>0.2306581399995858</v>
       </c>
       <c r="C64">
-        <v>-6552.168711076891</v>
+        <v>-6894.716565442255</v>
       </c>
       <c r="D64">
-        <v>8959.865288923111</v>
+        <v>8867.774434557747</v>
       </c>
       <c r="E64">
-        <v>15436.034</v>
+        <v>15686.491</v>
       </c>
       <c r="F64">
-        <v>15528.334</v>
+        <v>15778.791</v>
       </c>
       <c r="G64">
         <v>16.3</v>
@@ -6529,37 +6529,37 @@
         <v>29</v>
       </c>
       <c r="M64">
-        <v>3661.5811572</v>
+        <v>3720.6389178</v>
       </c>
       <c r="N64">
-        <v>-3632.5811572</v>
+        <v>-3691.6389178</v>
       </c>
       <c r="O64">
-        <v>-908.1452893000001</v>
+        <v>-922.9097294500001</v>
       </c>
       <c r="P64">
-        <v>-2724.4358679</v>
+        <v>-2768.72918835</v>
       </c>
       <c r="Q64">
-        <v>-2723.6358679</v>
+        <v>-2767.92918835</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2180305548602026</v>
+        <v>0.2226854347212892</v>
       </c>
       <c r="T64">
-        <v>2.506164429764459</v>
+        <v>2.573898603541877</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.001980018928637937</v>
+        <v>0.001948590056754794</v>
       </c>
       <c r="W64">
-        <v>0.2353331115366272</v>
+        <v>0.2353405224646172</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.007920075714551778</v>
+        <v>0.007794360227019181</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2306581399995858</v>
+        <v>0.2325581399995858</v>
       </c>
       <c r="C65">
-        <v>-6894.716565442255</v>
+        <v>-7235.390631352728</v>
       </c>
       <c r="D65">
-        <v>8867.774434557747</v>
+        <v>8777.557368647274</v>
       </c>
       <c r="E65">
-        <v>15686.491</v>
+        <v>15936.948</v>
       </c>
       <c r="F65">
-        <v>15778.791</v>
+        <v>16029.248</v>
       </c>
       <c r="G65">
         <v>16.3</v>
@@ -6611,37 +6611,37 @@
         <v>29</v>
       </c>
       <c r="M65">
-        <v>3720.6389178</v>
+        <v>3779.696678400001</v>
       </c>
       <c r="N65">
-        <v>-3691.6389178</v>
+        <v>-3750.696678400001</v>
       </c>
       <c r="O65">
-        <v>-922.9097294500001</v>
+        <v>-937.6741696000001</v>
       </c>
       <c r="P65">
-        <v>-2768.72918835</v>
+        <v>-2813.022508800001</v>
       </c>
       <c r="Q65">
-        <v>-2767.92918835</v>
+        <v>-2812.2225088</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2226854347212892</v>
+        <v>0.2275989190191027</v>
       </c>
       <c r="T65">
-        <v>2.573898603541877</v>
+        <v>2.645395786973596</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.001948590056754794</v>
+        <v>0.001918143337118001</v>
       </c>
       <c r="W65">
-        <v>0.2353405224646172</v>
+        <v>0.2353477018011076</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.007794360227019181</v>
+        <v>0.007672573348472045</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2325581399995858</v>
+        <v>0.2344581399995858</v>
       </c>
       <c r="C66">
-        <v>-7235.390631352728</v>
+        <v>-7574.247522290199</v>
       </c>
       <c r="D66">
-        <v>8777.557368647274</v>
+        <v>8689.157477709803</v>
       </c>
       <c r="E66">
-        <v>15936.948</v>
+        <v>16187.405</v>
       </c>
       <c r="F66">
-        <v>16029.248</v>
+        <v>16279.705</v>
       </c>
       <c r="G66">
         <v>16.3</v>
@@ -6693,37 +6693,37 @@
         <v>29</v>
       </c>
       <c r="M66">
-        <v>3779.696678400001</v>
+        <v>3838.754439000001</v>
       </c>
       <c r="N66">
-        <v>-3750.696678400001</v>
+        <v>-3809.754439000001</v>
       </c>
       <c r="O66">
-        <v>-937.6741696000001</v>
+        <v>-952.4386097500002</v>
       </c>
       <c r="P66">
-        <v>-2813.022508800001</v>
+        <v>-2857.315829250001</v>
       </c>
       <c r="Q66">
-        <v>-2812.2225088</v>
+        <v>-2856.51582925</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2275989190191027</v>
+        <v>0.23279317384822</v>
       </c>
       <c r="T66">
-        <v>2.645395786973596</v>
+        <v>2.72097852374427</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.001918143337118001</v>
+        <v>0.001888633439623878</v>
       </c>
       <c r="W66">
-        <v>0.2353477018011076</v>
+        <v>0.2353546602349367</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.007672573348472045</v>
+        <v>0.007554533758495463</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2344581399995858</v>
+        <v>0.2363581399995859</v>
       </c>
       <c r="C67">
-        <v>-7574.247522290199</v>
+        <v>-7911.341593830071</v>
       </c>
       <c r="D67">
-        <v>8689.157477709803</v>
+        <v>8602.52040616993</v>
       </c>
       <c r="E67">
-        <v>16187.405</v>
+        <v>16437.862</v>
       </c>
       <c r="F67">
-        <v>16279.705</v>
+        <v>16530.162</v>
       </c>
       <c r="G67">
         <v>16.3</v>
@@ -6775,37 +6775,37 @@
         <v>29</v>
       </c>
       <c r="M67">
-        <v>3838.754439000001</v>
+        <v>3897.8121996</v>
       </c>
       <c r="N67">
-        <v>-3809.754439000001</v>
+        <v>-3868.8121996</v>
       </c>
       <c r="O67">
-        <v>-952.4386097500002</v>
+        <v>-967.2030499000001</v>
       </c>
       <c r="P67">
-        <v>-2857.315829250001</v>
+        <v>-2901.6091497</v>
       </c>
       <c r="Q67">
-        <v>-2856.51582925</v>
+        <v>-2900.8091497</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.23279317384822</v>
+        <v>0.23829297307905</v>
       </c>
       <c r="T67">
-        <v>2.72097852374427</v>
+        <v>2.801007303854396</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.001888633439623878</v>
+        <v>0.001860017781447758</v>
       </c>
       <c r="W67">
-        <v>0.2353546602349367</v>
+        <v>0.2353614078071346</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.007554533758495463</v>
+        <v>0.007440071125791037</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2363581399995859</v>
+        <v>0.2382581399995858</v>
       </c>
       <c r="C68">
-        <v>-7911.341593830071</v>
+        <v>-8246.725055094625</v>
       </c>
       <c r="D68">
-        <v>8602.52040616993</v>
+        <v>8517.593944905379</v>
       </c>
       <c r="E68">
-        <v>16437.862</v>
+        <v>16688.319</v>
       </c>
       <c r="F68">
-        <v>16530.162</v>
+        <v>16780.619</v>
       </c>
       <c r="G68">
         <v>16.3</v>
@@ -6857,37 +6857,37 @@
         <v>29</v>
       </c>
       <c r="M68">
-        <v>3897.8121996</v>
+        <v>3956.869960200001</v>
       </c>
       <c r="N68">
-        <v>-3868.8121996</v>
+        <v>-3927.869960200001</v>
       </c>
       <c r="O68">
-        <v>-967.2030499000001</v>
+        <v>-981.9674900500002</v>
       </c>
       <c r="P68">
-        <v>-2901.6091497</v>
+        <v>-2945.90247015</v>
       </c>
       <c r="Q68">
-        <v>-2900.8091497</v>
+        <v>-2945.10247015</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.23829297307905</v>
+        <v>0.2441260934753848</v>
       </c>
       <c r="T68">
-        <v>2.801007303854396</v>
+        <v>2.885886313062105</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.001860017781447758</v>
+        <v>0.001832256322023165</v>
       </c>
       <c r="W68">
-        <v>0.2353614078071346</v>
+        <v>0.2353679539592669</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.007440071125791037</v>
+        <v>0.00732902528809265</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2382581399995858</v>
+        <v>0.2401581399995859</v>
       </c>
       <c r="C69">
-        <v>-8246.725055094625</v>
+        <v>-8580.448073669171</v>
       </c>
       <c r="D69">
-        <v>8517.593944905379</v>
+        <v>8434.32792633083</v>
       </c>
       <c r="E69">
-        <v>16688.319</v>
+        <v>16938.776</v>
       </c>
       <c r="F69">
-        <v>16780.619</v>
+        <v>17031.076</v>
       </c>
       <c r="G69">
         <v>16.3</v>
@@ -6939,37 +6939,37 @@
         <v>29</v>
       </c>
       <c r="M69">
-        <v>3956.869960200001</v>
+        <v>4015.9277208</v>
       </c>
       <c r="N69">
-        <v>-3927.869960200001</v>
+        <v>-3986.9277208</v>
       </c>
       <c r="O69">
-        <v>-981.9674900500002</v>
+        <v>-996.7319302000001</v>
       </c>
       <c r="P69">
-        <v>-2945.90247015</v>
+        <v>-2990.1957906</v>
       </c>
       <c r="Q69">
-        <v>-2945.10247015</v>
+        <v>-2989.3957906</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2441260934753848</v>
+        <v>0.2503237838964906</v>
       </c>
       <c r="T69">
-        <v>2.885886313062105</v>
+        <v>2.976070260345296</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.001832256322023165</v>
+        <v>0.00180531137611106</v>
       </c>
       <c r="W69">
-        <v>0.2353679539592669</v>
+        <v>0.235374307577513</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.00732902528809265</v>
+        <v>0.007221245504444251</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2401581399995859</v>
+        <v>0.2420581399995859</v>
       </c>
       <c r="C70">
-        <v>-8580.448073669171</v>
+        <v>-8912.558874423947</v>
       </c>
       <c r="D70">
-        <v>8434.32792633083</v>
+        <v>8352.674125576057</v>
       </c>
       <c r="E70">
-        <v>16938.776</v>
+        <v>17189.233</v>
       </c>
       <c r="F70">
-        <v>17031.076</v>
+        <v>17281.533</v>
       </c>
       <c r="G70">
         <v>16.3</v>
@@ -7021,37 +7021,37 @@
         <v>29</v>
       </c>
       <c r="M70">
-        <v>4015.9277208</v>
+        <v>4074.985481400001</v>
       </c>
       <c r="N70">
-        <v>-3986.9277208</v>
+        <v>-4045.985481400001</v>
       </c>
       <c r="O70">
-        <v>-996.7319302000001</v>
+        <v>-1011.49637035</v>
       </c>
       <c r="P70">
-        <v>-2990.1957906</v>
+        <v>-3034.489111050001</v>
       </c>
       <c r="Q70">
-        <v>-2989.3957906</v>
+        <v>-3033.689111050001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2503237838964906</v>
+        <v>0.2569213253125064</v>
       </c>
       <c r="T70">
-        <v>2.976070260345296</v>
+        <v>3.072072526808047</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.00180531137611106</v>
+        <v>0.001779147443123943</v>
       </c>
       <c r="W70">
-        <v>0.235374307577513</v>
+        <v>0.2353804770329114</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.007221245504444251</v>
+        <v>0.007116589772495741</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2420581399995859</v>
+        <v>0.2439581399995858</v>
       </c>
       <c r="C71">
-        <v>-8912.558874423947</v>
+        <v>-9243.103832650784</v>
       </c>
       <c r="D71">
-        <v>8352.674125576057</v>
+        <v>8272.586167349218</v>
       </c>
       <c r="E71">
-        <v>17189.233</v>
+        <v>17439.69</v>
       </c>
       <c r="F71">
-        <v>17281.533</v>
+        <v>17531.99</v>
       </c>
       <c r="G71">
         <v>16.3</v>
@@ -7103,37 +7103,37 @@
         <v>29</v>
       </c>
       <c r="M71">
-        <v>4074.985481400001</v>
+        <v>4134.043242000001</v>
       </c>
       <c r="N71">
-        <v>-4045.985481400001</v>
+        <v>-4105.043242000001</v>
       </c>
       <c r="O71">
-        <v>-1011.49637035</v>
+        <v>-1026.2608105</v>
       </c>
       <c r="P71">
-        <v>-3034.489111050001</v>
+        <v>-3078.782431500001</v>
       </c>
       <c r="Q71">
-        <v>-3033.689111050001</v>
+        <v>-3077.982431500001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2569213253125064</v>
+        <v>0.2639587028229233</v>
       </c>
       <c r="T71">
-        <v>3.072072526808047</v>
+        <v>3.174474944368316</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.001779147443123943</v>
+        <v>0.001753731051079315</v>
       </c>
       <c r="W71">
-        <v>0.2353804770329114</v>
+        <v>0.2353864702181555</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.007116589772495741</v>
+        <v>0.007014924204317263</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2439581399995858</v>
+        <v>0.2458581399995858</v>
       </c>
       <c r="C72">
-        <v>-9243.103832650784</v>
+        <v>-9572.127561892576</v>
       </c>
       <c r="D72">
-        <v>8272.586167349218</v>
+        <v>8194.019438107429</v>
       </c>
       <c r="E72">
-        <v>17439.69</v>
+        <v>17690.147</v>
       </c>
       <c r="F72">
-        <v>17531.99</v>
+        <v>17782.447</v>
       </c>
       <c r="G72">
         <v>16.3</v>
@@ -7185,37 +7185,37 @@
         <v>29</v>
       </c>
       <c r="M72">
-        <v>4134.043242000001</v>
+        <v>4193.101002600001</v>
       </c>
       <c r="N72">
-        <v>-4105.043242000001</v>
+        <v>-4164.101002600001</v>
       </c>
       <c r="O72">
-        <v>-1026.2608105</v>
+        <v>-1041.02525065</v>
       </c>
       <c r="P72">
-        <v>-3078.782431500001</v>
+        <v>-3123.075751950001</v>
       </c>
       <c r="Q72">
-        <v>-3077.982431500001</v>
+        <v>-3122.275751950001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2639587028229233</v>
+        <v>0.271481416713369</v>
       </c>
       <c r="T72">
-        <v>3.174474944368316</v>
+        <v>3.283939597622396</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.001753731051079315</v>
+        <v>0.001729030613740169</v>
       </c>
       <c r="W72">
-        <v>0.2353864702181555</v>
+        <v>0.2353922945812801</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.007014924204317263</v>
+        <v>0.006916122454960649</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2458581399995858</v>
+        <v>0.2477581399995858</v>
       </c>
       <c r="C73">
-        <v>-9572.127561892572</v>
+        <v>-9899.672996814954</v>
       </c>
       <c r="D73">
-        <v>8194.019438107429</v>
+        <v>8116.931003185045</v>
       </c>
       <c r="E73">
-        <v>17690.147</v>
+        <v>17940.604</v>
       </c>
       <c r="F73">
-        <v>17782.447</v>
+        <v>18032.904</v>
       </c>
       <c r="G73">
         <v>16.3</v>
@@ -7267,37 +7267,37 @@
         <v>29</v>
       </c>
       <c r="M73">
-        <v>4193.1010026</v>
+        <v>4252.1587632</v>
       </c>
       <c r="N73">
-        <v>-4164.1010026</v>
+        <v>-4223.1587632</v>
       </c>
       <c r="O73">
-        <v>-1041.02525065</v>
+        <v>-1055.7896908</v>
       </c>
       <c r="P73">
-        <v>-3123.07575195</v>
+        <v>-3167.3690724</v>
       </c>
       <c r="Q73">
-        <v>-3122.27575195</v>
+        <v>-3166.5690724</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2714814167133689</v>
+        <v>0.2795414673102749</v>
       </c>
       <c r="T73">
-        <v>3.283939597622394</v>
+        <v>3.401223154680337</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.00172903061374017</v>
+        <v>0.001705016299660445</v>
       </c>
       <c r="W73">
-        <v>0.2353922945812801</v>
+        <v>0.2353979571565401</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.006916122454960649</v>
+        <v>0.006820065198641756</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2477581399995858</v>
+        <v>0.2496581399995858</v>
       </c>
       <c r="C74">
-        <v>-9899.672996814954</v>
+        <v>-10225.78147144375</v>
       </c>
       <c r="D74">
-        <v>8116.931003185045</v>
+        <v>8041.279528556253</v>
       </c>
       <c r="E74">
-        <v>17940.604</v>
+        <v>18191.061</v>
       </c>
       <c r="F74">
-        <v>18032.904</v>
+        <v>18283.361</v>
       </c>
       <c r="G74">
         <v>16.3</v>
@@ -7349,37 +7349,37 @@
         <v>29</v>
       </c>
       <c r="M74">
-        <v>4252.1587632</v>
+        <v>4311.216523800001</v>
       </c>
       <c r="N74">
-        <v>-4223.1587632</v>
+        <v>-4282.216523800001</v>
       </c>
       <c r="O74">
-        <v>-1055.7896908</v>
+        <v>-1070.55413095</v>
       </c>
       <c r="P74">
-        <v>-3167.3690724</v>
+        <v>-3211.66239285</v>
       </c>
       <c r="Q74">
-        <v>-3166.5690724</v>
+        <v>-3210.86239285</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2795414673102749</v>
+        <v>0.288198558692137</v>
       </c>
       <c r="T74">
-        <v>3.401223154680337</v>
+        <v>3.52719438263146</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.001705016299660445</v>
+        <v>0.001681659911993864</v>
       </c>
       <c r="W74">
-        <v>0.2353979571565401</v>
+        <v>0.2354034645927519</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.006820065198641756</v>
+        <v>0.006726639647975485</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2496581399995858</v>
+        <v>0.2515581399995858</v>
       </c>
       <c r="C75">
-        <v>-10225.78147144375</v>
+        <v>-10550.49279306761</v>
       </c>
       <c r="D75">
-        <v>8041.279528556253</v>
+        <v>7967.025206932391</v>
       </c>
       <c r="E75">
-        <v>18191.061</v>
+        <v>18441.518</v>
       </c>
       <c r="F75">
-        <v>18283.361</v>
+        <v>18533.818</v>
       </c>
       <c r="G75">
         <v>16.3</v>
@@ -7431,37 +7431,37 @@
         <v>29</v>
       </c>
       <c r="M75">
-        <v>4311.216523800001</v>
+        <v>4370.2742844</v>
       </c>
       <c r="N75">
-        <v>-4282.216523800001</v>
+        <v>-4341.2742844</v>
       </c>
       <c r="O75">
-        <v>-1070.55413095</v>
+        <v>-1085.3185711</v>
       </c>
       <c r="P75">
-        <v>-3211.66239285</v>
+        <v>-3255.9557133</v>
       </c>
       <c r="Q75">
-        <v>-3210.86239285</v>
+        <v>-3255.1557133</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.288198558692137</v>
+        <v>0.2975215801802961</v>
       </c>
       <c r="T75">
-        <v>3.52719438263146</v>
+        <v>3.662855705040363</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.001681659911993864</v>
+        <v>0.001658934778048001</v>
       </c>
       <c r="W75">
-        <v>0.2354034645927519</v>
+        <v>0.2354088231793363</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.006726639647975485</v>
+        <v>0.006635739112191952</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2515581399995858</v>
+        <v>0.2534581399995859</v>
       </c>
       <c r="C76">
-        <v>-10550.49279306761</v>
+        <v>-10873.84531208363</v>
       </c>
       <c r="D76">
-        <v>7967.025206932391</v>
+        <v>7894.129687916366</v>
       </c>
       <c r="E76">
-        <v>18441.518</v>
+        <v>18691.975</v>
       </c>
       <c r="F76">
-        <v>18533.818</v>
+        <v>18784.275</v>
       </c>
       <c r="G76">
         <v>16.3</v>
@@ -7513,37 +7513,37 @@
         <v>29</v>
       </c>
       <c r="M76">
-        <v>4370.2742844</v>
+        <v>4429.332045</v>
       </c>
       <c r="N76">
-        <v>-4341.2742844</v>
+        <v>-4400.332045</v>
       </c>
       <c r="O76">
-        <v>-1085.3185711</v>
+        <v>-1100.08301125</v>
       </c>
       <c r="P76">
-        <v>-3255.9557133</v>
+        <v>-3300.24903375</v>
       </c>
       <c r="Q76">
-        <v>-3255.1557133</v>
+        <v>-3299.44903375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2975215801802961</v>
+        <v>0.307590443387508</v>
       </c>
       <c r="T76">
-        <v>3.662855705040363</v>
+        <v>3.809369933241978</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.001658934778048001</v>
+        <v>0.001636815647674027</v>
       </c>
       <c r="W76">
-        <v>0.2354088231793363</v>
+        <v>0.2354140388702785</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.006635739112191952</v>
+        <v>0.006547262590696157</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2534581399995859</v>
+        <v>0.2553581399995858</v>
       </c>
       <c r="C77">
-        <v>-10873.84531208363</v>
+        <v>-11195.8759880433</v>
       </c>
       <c r="D77">
-        <v>7894.129687916366</v>
+        <v>7822.556011956699</v>
       </c>
       <c r="E77">
-        <v>18691.975</v>
+        <v>18942.432</v>
       </c>
       <c r="F77">
-        <v>18784.275</v>
+        <v>19034.732</v>
       </c>
       <c r="G77">
         <v>16.3</v>
@@ -7595,37 +7595,37 @@
         <v>29</v>
       </c>
       <c r="M77">
-        <v>4429.332045</v>
+        <v>4488.3898056</v>
       </c>
       <c r="N77">
-        <v>-4400.332045</v>
+        <v>-4459.3898056</v>
       </c>
       <c r="O77">
-        <v>-1100.08301125</v>
+        <v>-1114.8474514</v>
       </c>
       <c r="P77">
-        <v>-3300.24903375</v>
+        <v>-3344.5423542</v>
       </c>
       <c r="Q77">
-        <v>-3299.44903375</v>
+        <v>-3343.7423542</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.307590443387508</v>
+        <v>0.3184983785286541</v>
       </c>
       <c r="T77">
-        <v>3.809369933241978</v>
+        <v>3.968093680460393</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.001636815647674027</v>
+        <v>0.001615278599678317</v>
       </c>
       <c r="W77">
-        <v>0.2354140388702785</v>
+        <v>0.2354191173061959</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.006547262590696157</v>
+        <v>0.006461114398713219</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2553581399995858</v>
+        <v>0.2572581399995859</v>
       </c>
       <c r="C78">
-        <v>-11195.8759880433</v>
+        <v>-11516.62045213783</v>
       </c>
       <c r="D78">
-        <v>7822.556011956699</v>
+        <v>7752.268547862166</v>
       </c>
       <c r="E78">
-        <v>18942.432</v>
+        <v>19192.889</v>
       </c>
       <c r="F78">
-        <v>19034.732</v>
+        <v>19285.189</v>
       </c>
       <c r="G78">
         <v>16.3</v>
@@ -7677,37 +7677,37 @@
         <v>29</v>
       </c>
       <c r="M78">
-        <v>4488.3898056</v>
+        <v>4547.4475662</v>
       </c>
       <c r="N78">
-        <v>-4459.3898056</v>
+        <v>-4518.4475662</v>
       </c>
       <c r="O78">
-        <v>-1114.8474514</v>
+        <v>-1129.61189155</v>
       </c>
       <c r="P78">
-        <v>-3344.5423542</v>
+        <v>-3388.83567465</v>
       </c>
       <c r="Q78">
-        <v>-3343.7423542</v>
+        <v>-3388.03567465</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3184983785286541</v>
+        <v>0.3303548297690304</v>
       </c>
       <c r="T78">
-        <v>3.968093680460393</v>
+        <v>4.140619492654324</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.001615278599678317</v>
+        <v>0.00159430095552665</v>
       </c>
       <c r="W78">
-        <v>0.2354191173061959</v>
+        <v>0.2354240638346868</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.006461114398713219</v>
+        <v>0.006377203822106603</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2572581399995859</v>
+        <v>0.2591581399995858</v>
       </c>
       <c r="C79">
-        <v>-11516.62045213783</v>
+        <v>-11836.11306634485</v>
       </c>
       <c r="D79">
-        <v>7752.268547862166</v>
+        <v>7683.23293365515</v>
       </c>
       <c r="E79">
-        <v>19192.889</v>
+        <v>19443.346</v>
       </c>
       <c r="F79">
-        <v>19285.189</v>
+        <v>19535.646</v>
       </c>
       <c r="G79">
         <v>16.3</v>
@@ -7759,37 +7759,37 @@
         <v>29</v>
       </c>
       <c r="M79">
-        <v>4547.4475662</v>
+        <v>4606.5053268</v>
       </c>
       <c r="N79">
-        <v>-4518.4475662</v>
+        <v>-4577.5053268</v>
       </c>
       <c r="O79">
-        <v>-1129.61189155</v>
+        <v>-1144.3763317</v>
       </c>
       <c r="P79">
-        <v>-3388.83567465</v>
+        <v>-3433.1289951</v>
       </c>
       <c r="Q79">
-        <v>-3388.03567465</v>
+        <v>-3432.3289951</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3303548297690304</v>
+        <v>0.3432891402130772</v>
       </c>
       <c r="T79">
-        <v>4.140619492654324</v>
+        <v>4.328829469593157</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.00159430095552665</v>
+        <v>0.001573861199686565</v>
       </c>
       <c r="W79">
-        <v>0.2354240638346868</v>
+        <v>0.2354288835291139</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.006377203822106603</v>
+        <v>0.006295444798746219</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2591581399995858</v>
+        <v>0.2610581399995858</v>
       </c>
       <c r="C80">
-        <v>-11836.11306634485</v>
+        <v>-12154.38697944265</v>
       </c>
       <c r="D80">
-        <v>7683.23293365515</v>
+        <v>7615.416020557355</v>
       </c>
       <c r="E80">
-        <v>19443.346</v>
+        <v>19693.803</v>
       </c>
       <c r="F80">
-        <v>19535.646</v>
+        <v>19786.103</v>
       </c>
       <c r="G80">
         <v>16.3</v>
@@ -7841,37 +7841,37 @@
         <v>29</v>
       </c>
       <c r="M80">
-        <v>4606.5053268</v>
+        <v>4665.563087400001</v>
       </c>
       <c r="N80">
-        <v>-4577.5053268</v>
+        <v>-4636.563087400001</v>
       </c>
       <c r="O80">
-        <v>-1144.3763317</v>
+        <v>-1159.14077185</v>
       </c>
       <c r="P80">
-        <v>-3433.1289951</v>
+        <v>-3477.42231555</v>
       </c>
       <c r="Q80">
-        <v>-3432.3289951</v>
+        <v>-3476.62231555</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3432891402130772</v>
+        <v>0.3574552897470333</v>
       </c>
       <c r="T80">
-        <v>4.328829469593157</v>
+        <v>4.534964206240451</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.001573861199686565</v>
+        <v>0.001553938906019646</v>
       </c>
       <c r="W80">
-        <v>0.2354288835291139</v>
+        <v>0.2354335812059606</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.006295444798746219</v>
+        <v>0.006215755624078612</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2610581399995858</v>
+        <v>0.2629581399995858</v>
       </c>
       <c r="C81">
-        <v>-12154.38697944265</v>
+        <v>-12471.47418008392</v>
       </c>
       <c r="D81">
-        <v>7615.416020557355</v>
+        <v>7548.785819916077</v>
       </c>
       <c r="E81">
-        <v>19693.803</v>
+        <v>19944.26</v>
       </c>
       <c r="F81">
-        <v>19786.103</v>
+        <v>20036.56</v>
       </c>
       <c r="G81">
         <v>16.3</v>
@@ -7923,37 +7923,37 @@
         <v>29</v>
       </c>
       <c r="M81">
-        <v>4665.563087400001</v>
+        <v>4724.620848</v>
       </c>
       <c r="N81">
-        <v>-4636.563087400001</v>
+        <v>-4695.620848</v>
       </c>
       <c r="O81">
-        <v>-1159.14077185</v>
+        <v>-1173.905212</v>
       </c>
       <c r="P81">
-        <v>-3477.42231555</v>
+        <v>-3521.715636</v>
       </c>
       <c r="Q81">
-        <v>-3476.62231555</v>
+        <v>-3520.915636</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3574552897470333</v>
+        <v>0.373038054234385</v>
       </c>
       <c r="T81">
-        <v>4.534964206240451</v>
+        <v>4.761712416552473</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.001553938906019646</v>
+        <v>0.001534514669694401</v>
       </c>
       <c r="W81">
-        <v>0.2354335812059606</v>
+        <v>0.2354381614408861</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.006215755624078612</v>
+        <v>0.006138058678777591</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2629581399995858</v>
+        <v>0.2648581399995859</v>
       </c>
       <c r="C82">
-        <v>-12471.47418008392</v>
+        <v>-12787.40554710753</v>
       </c>
       <c r="D82">
-        <v>7548.785819916077</v>
+        <v>7483.311452892475</v>
       </c>
       <c r="E82">
-        <v>19944.26</v>
+        <v>20194.717</v>
       </c>
       <c r="F82">
-        <v>20036.56</v>
+        <v>20287.017</v>
       </c>
       <c r="G82">
         <v>16.3</v>
@@ -8005,37 +8005,37 @@
         <v>29</v>
       </c>
       <c r="M82">
-        <v>4724.620848</v>
+        <v>4783.678608600001</v>
       </c>
       <c r="N82">
-        <v>-4695.620848</v>
+        <v>-4754.678608600001</v>
       </c>
       <c r="O82">
-        <v>-1173.905212</v>
+        <v>-1188.66965215</v>
       </c>
       <c r="P82">
-        <v>-3521.715636</v>
+        <v>-3566.008956450001</v>
       </c>
       <c r="Q82">
-        <v>-3520.915636</v>
+        <v>-3565.208956450001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.373038054234385</v>
+        <v>0.3902611097204052</v>
       </c>
       <c r="T82">
-        <v>4.761712416552473</v>
+        <v>5.012328859528919</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.001534514669694401</v>
+        <v>0.001515570044142618</v>
       </c>
       <c r="W82">
-        <v>0.2354381614408861</v>
+        <v>0.2354426285835912</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.006138058678777591</v>
+        <v>0.006062280176570511</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2648581399995859</v>
+        <v>0.2667581399995859</v>
       </c>
       <c r="C83">
-        <v>-12787.40554710753</v>
+        <v>-13102.2108972544</v>
       </c>
       <c r="D83">
-        <v>7483.311452892475</v>
+        <v>7418.963102745599</v>
       </c>
       <c r="E83">
-        <v>20194.717</v>
+        <v>20445.174</v>
       </c>
       <c r="F83">
-        <v>20287.017</v>
+        <v>20537.474</v>
       </c>
       <c r="G83">
         <v>16.3</v>
@@ -8087,37 +8087,37 @@
         <v>29</v>
       </c>
       <c r="M83">
-        <v>4783.678608600001</v>
+        <v>4842.736369200001</v>
       </c>
       <c r="N83">
-        <v>-4754.678608600001</v>
+        <v>-4813.736369200001</v>
       </c>
       <c r="O83">
-        <v>-1188.66965215</v>
+        <v>-1203.4340923</v>
       </c>
       <c r="P83">
-        <v>-3566.008956450001</v>
+        <v>-3610.302276900001</v>
       </c>
       <c r="Q83">
-        <v>-3565.208956450001</v>
+        <v>-3609.502276900001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3902611097204052</v>
+        <v>0.4093978380382056</v>
       </c>
       <c r="T83">
-        <v>5.012328859528919</v>
+        <v>5.290791573947193</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.001515570044142618</v>
+        <v>0.001497087482628684</v>
       </c>
       <c r="W83">
-        <v>0.2354426285835912</v>
+        <v>0.2354469867715962</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.006062280176570511</v>
+        <v>0.00598834993051478</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2667581399995859</v>
+        <v>0.2686581399995859</v>
       </c>
       <c r="C84">
-        <v>-13102.2108972544</v>
+        <v>-13415.91903044273</v>
       </c>
       <c r="D84">
-        <v>7418.963102745599</v>
+        <v>7355.711969557273</v>
       </c>
       <c r="E84">
-        <v>20445.174</v>
+        <v>20695.631</v>
       </c>
       <c r="F84">
-        <v>20537.474</v>
+        <v>20787.931</v>
       </c>
       <c r="G84">
         <v>16.3</v>
@@ -8169,37 +8169,37 @@
         <v>29</v>
       </c>
       <c r="M84">
-        <v>4842.736369200001</v>
+        <v>4901.794129800001</v>
       </c>
       <c r="N84">
-        <v>-4813.736369200001</v>
+        <v>-4872.794129800001</v>
       </c>
       <c r="O84">
-        <v>-1203.4340923</v>
+        <v>-1218.19853245</v>
       </c>
       <c r="P84">
-        <v>-3610.302276900001</v>
+        <v>-3654.595597350001</v>
       </c>
       <c r="Q84">
-        <v>-3609.502276900001</v>
+        <v>-3653.795597350001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4093978380382056</v>
+        <v>0.4307859461581001</v>
       </c>
       <c r="T84">
-        <v>5.290791573947193</v>
+        <v>5.602014607708793</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.001497087482628684</v>
+        <v>0.001479050284042796</v>
       </c>
       <c r="W84">
-        <v>0.2354469867715962</v>
+        <v>0.2354512399430227</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.00598834993051478</v>
+        <v>0.005916201136171195</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2686581399995859</v>
+        <v>0.2705581399995859</v>
       </c>
       <c r="C85">
-        <v>-13415.91903044273</v>
+        <v>-13728.55777274663</v>
       </c>
       <c r="D85">
-        <v>7355.711969557273</v>
+        <v>7293.530227253369</v>
       </c>
       <c r="E85">
-        <v>20695.631</v>
+        <v>20946.088</v>
       </c>
       <c r="F85">
-        <v>20787.931</v>
+        <v>21038.388</v>
       </c>
       <c r="G85">
         <v>16.3</v>
@@ -8251,37 +8251,37 @@
         <v>29</v>
       </c>
       <c r="M85">
-        <v>4901.794129800001</v>
+        <v>4960.851890400001</v>
       </c>
       <c r="N85">
-        <v>-4872.794129800001</v>
+        <v>-4931.851890400001</v>
       </c>
       <c r="O85">
-        <v>-1218.19853245</v>
+        <v>-1232.9629726</v>
       </c>
       <c r="P85">
-        <v>-3654.595597350001</v>
+        <v>-3698.888917800001</v>
       </c>
       <c r="Q85">
-        <v>-3653.795597350001</v>
+        <v>-3698.088917800001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4307859461581001</v>
+        <v>0.4548475677929814</v>
       </c>
       <c r="T85">
-        <v>5.602014607708793</v>
+        <v>5.952140520690594</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.001479050284042796</v>
+        <v>0.001461442542566096</v>
       </c>
       <c r="W85">
-        <v>0.2354512399430227</v>
+        <v>0.2354553918484629</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.005916201136171195</v>
+        <v>0.005845770170264331</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2705581399995858</v>
+        <v>0.2724581399995858</v>
       </c>
       <c r="C86">
-        <v>-13728.55777274663</v>
+        <v>-14040.15401721324</v>
       </c>
       <c r="D86">
-        <v>7293.530227253369</v>
+        <v>7232.390982786763</v>
       </c>
       <c r="E86">
-        <v>20946.088</v>
+        <v>21196.545</v>
       </c>
       <c r="F86">
-        <v>21038.388</v>
+        <v>21288.845</v>
       </c>
       <c r="G86">
         <v>16.3</v>
@@ -8333,37 +8333,37 @@
         <v>29</v>
       </c>
       <c r="M86">
-        <v>4960.8518904</v>
+        <v>5019.909651000001</v>
       </c>
       <c r="N86">
-        <v>-4931.8518904</v>
+        <v>-4990.909651000001</v>
       </c>
       <c r="O86">
-        <v>-1232.9629726</v>
+        <v>-1247.72741275</v>
       </c>
       <c r="P86">
-        <v>-3698.8889178</v>
+        <v>-3743.18223825</v>
       </c>
       <c r="Q86">
-        <v>-3698.0889178</v>
+        <v>-3742.38223825</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4548475677929811</v>
+        <v>0.4821174056458466</v>
       </c>
       <c r="T86">
-        <v>5.952140520690589</v>
+        <v>6.34894988873663</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.001461442542566096</v>
+        <v>0.001444249100888848</v>
       </c>
       <c r="W86">
-        <v>0.2354553918484629</v>
+        <v>0.2354594460620104</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.005845770170264331</v>
+        <v>0.005776996403555446</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2724581399995858</v>
+        <v>0.2743581399995859</v>
       </c>
       <c r="C87">
-        <v>-14040.15401721324</v>
+        <v>-14350.73376264387</v>
       </c>
       <c r="D87">
-        <v>7232.390982786763</v>
+        <v>7172.268237356124</v>
       </c>
       <c r="E87">
-        <v>21196.545</v>
+        <v>21447.002</v>
       </c>
       <c r="F87">
-        <v>21288.845</v>
+        <v>21539.302</v>
       </c>
       <c r="G87">
         <v>16.3</v>
@@ -8415,37 +8415,37 @@
         <v>29</v>
       </c>
       <c r="M87">
-        <v>5019.909651000001</v>
+        <v>5078.967411600001</v>
       </c>
       <c r="N87">
-        <v>-4990.909651000001</v>
+        <v>-5049.967411600001</v>
       </c>
       <c r="O87">
-        <v>-1247.72741275</v>
+        <v>-1262.4918529</v>
       </c>
       <c r="P87">
-        <v>-3743.18223825</v>
+        <v>-3787.4755587</v>
       </c>
       <c r="Q87">
-        <v>-3742.38223825</v>
+        <v>-3786.6755587</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4821174056458466</v>
+        <v>0.5132829346205499</v>
       </c>
       <c r="T87">
-        <v>6.34894988873663</v>
+        <v>6.802446309360675</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.001444249100888848</v>
+        <v>0.001427455506692466</v>
       </c>
       <c r="W87">
-        <v>0.2354594460620104</v>
+        <v>0.2354634059915219</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.005776996403555446</v>
+        <v>0.00570982202676984</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2743581399995859</v>
+        <v>0.2762581399995858</v>
       </c>
       <c r="C88">
-        <v>-14350.73376264387</v>
+        <v>-14660.32215045687</v>
       </c>
       <c r="D88">
-        <v>7172.268237356124</v>
+        <v>7113.136849543132</v>
       </c>
       <c r="E88">
-        <v>21447.002</v>
+        <v>21697.459</v>
       </c>
       <c r="F88">
-        <v>21539.302</v>
+        <v>21789.759</v>
       </c>
       <c r="G88">
         <v>16.3</v>
@@ -8497,37 +8497,37 @@
         <v>29</v>
       </c>
       <c r="M88">
-        <v>5078.967411600001</v>
+        <v>5138.0251722</v>
       </c>
       <c r="N88">
-        <v>-5049.967411600001</v>
+        <v>-5109.0251722</v>
       </c>
       <c r="O88">
-        <v>-1262.4918529</v>
+        <v>-1277.25629305</v>
       </c>
       <c r="P88">
-        <v>-3787.4755587</v>
+        <v>-3831.76887915</v>
       </c>
       <c r="Q88">
-        <v>-3786.6755587</v>
+        <v>-3830.96887915</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5132829346205499</v>
+        <v>0.5492431603605921</v>
       </c>
       <c r="T88">
-        <v>6.802446309360675</v>
+        <v>7.325711410080726</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.001427455506692466</v>
+        <v>0.001411047972132782</v>
       </c>
       <c r="W88">
-        <v>0.2354634059915219</v>
+        <v>0.2354672748881711</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.00570982202676984</v>
+        <v>0.005644191888531158</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2762581399995858</v>
+        <v>0.2781581399995858</v>
       </c>
       <c r="C89">
-        <v>-14660.32215045687</v>
+        <v>-14968.9434997418</v>
       </c>
       <c r="D89">
-        <v>7113.136849543132</v>
+        <v>7054.972500258204</v>
       </c>
       <c r="E89">
-        <v>21697.459</v>
+        <v>21947.916</v>
       </c>
       <c r="F89">
-        <v>21789.759</v>
+        <v>22040.216</v>
       </c>
       <c r="G89">
         <v>16.3</v>
@@ -8579,37 +8579,37 @@
         <v>29</v>
       </c>
       <c r="M89">
-        <v>5138.0251722</v>
+        <v>5197.0829328</v>
       </c>
       <c r="N89">
-        <v>-5109.0251722</v>
+        <v>-5168.0829328</v>
       </c>
       <c r="O89">
-        <v>-1277.25629305</v>
+        <v>-1292.0207332</v>
       </c>
       <c r="P89">
-        <v>-3831.76887915</v>
+        <v>-3876.0621996</v>
       </c>
       <c r="Q89">
-        <v>-3830.96887915</v>
+        <v>-3875.2621996</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5492431603605921</v>
+        <v>0.5911967570573081</v>
       </c>
       <c r="T89">
-        <v>7.325711410080726</v>
+        <v>7.936187360920787</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.001411047972132782</v>
+        <v>0.001395013336085819</v>
       </c>
       <c r="W89">
-        <v>0.2354672748881711</v>
+        <v>0.235471055855351</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.005644191888531158</v>
+        <v>0.005580053344343305</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2781581399995858</v>
+        <v>0.2800581399995858</v>
       </c>
       <c r="C90">
-        <v>-14968.9434997418</v>
+        <v>-15276.62134060784</v>
       </c>
       <c r="D90">
-        <v>7054.972500258204</v>
+        <v>6997.751659392165</v>
       </c>
       <c r="E90">
-        <v>21947.916</v>
+        <v>22198.373</v>
       </c>
       <c r="F90">
-        <v>22040.216</v>
+        <v>22290.673</v>
       </c>
       <c r="G90">
         <v>16.3</v>
@@ -8661,37 +8661,37 @@
         <v>29</v>
       </c>
       <c r="M90">
-        <v>5197.0829328</v>
+        <v>5256.140693400001</v>
       </c>
       <c r="N90">
-        <v>-5168.0829328</v>
+        <v>-5227.140693400001</v>
       </c>
       <c r="O90">
-        <v>-1292.0207332</v>
+        <v>-1306.78517335</v>
       </c>
       <c r="P90">
-        <v>-3876.0621996</v>
+        <v>-3920.35552005</v>
       </c>
       <c r="Q90">
-        <v>-3875.2621996</v>
+        <v>-3919.55552005</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5911967570573081</v>
+        <v>0.6407782804261544</v>
       </c>
       <c r="T90">
-        <v>7.936187360920787</v>
+        <v>8.657658939186314</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.001395013336085819</v>
+        <v>0.001379339028938787</v>
       </c>
       <c r="W90">
-        <v>0.235471055855351</v>
+        <v>0.2354747518569762</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.005580053344343305</v>
+        <v>0.005517356115755101</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2800581399995858</v>
+        <v>0.2819581399995859</v>
       </c>
       <c r="C91">
-        <v>-15276.62134060784</v>
+        <v>-15583.3784459223</v>
       </c>
       <c r="D91">
-        <v>6997.751659392165</v>
+        <v>6941.451554077699</v>
       </c>
       <c r="E91">
-        <v>22198.373</v>
+        <v>22448.83</v>
       </c>
       <c r="F91">
-        <v>22290.673</v>
+        <v>22541.13</v>
       </c>
       <c r="G91">
         <v>16.3</v>
@@ -8743,37 +8743,37 @@
         <v>29</v>
       </c>
       <c r="M91">
-        <v>5256.140693400001</v>
+        <v>5315.198454</v>
       </c>
       <c r="N91">
-        <v>-5227.140693400001</v>
+        <v>-5286.198454</v>
       </c>
       <c r="O91">
-        <v>-1306.78517335</v>
+        <v>-1321.5496135</v>
       </c>
       <c r="P91">
-        <v>-3920.35552005</v>
+        <v>-3964.6488405</v>
       </c>
       <c r="Q91">
-        <v>-3919.55552005</v>
+        <v>-3963.8488405</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6407782804261544</v>
+        <v>0.70027610846877</v>
       </c>
       <c r="T91">
-        <v>8.657658939186314</v>
+        <v>9.523424833104947</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.001379339028938787</v>
+        <v>0.001364013039728356</v>
       </c>
       <c r="W91">
-        <v>0.2354747518569762</v>
+        <v>0.2354783657252321</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.005517356115755101</v>
+        <v>0.005456052158913427</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2819581399995859</v>
+        <v>0.2838581399995858</v>
       </c>
       <c r="C92">
-        <v>-15583.3784459223</v>
+        <v>-15889.23686152931</v>
       </c>
       <c r="D92">
-        <v>6941.451554077699</v>
+        <v>6886.050138470696</v>
       </c>
       <c r="E92">
-        <v>22448.83</v>
+        <v>22699.287</v>
       </c>
       <c r="F92">
-        <v>22541.13</v>
+        <v>22791.587</v>
       </c>
       <c r="G92">
         <v>16.3</v>
@@ -8825,37 +8825,37 @@
         <v>29</v>
       </c>
       <c r="M92">
-        <v>5315.198454</v>
+        <v>5374.256214600001</v>
       </c>
       <c r="N92">
-        <v>-5286.198454</v>
+        <v>-5345.256214600001</v>
       </c>
       <c r="O92">
-        <v>-1321.5496135</v>
+        <v>-1336.31405365</v>
       </c>
       <c r="P92">
-        <v>-3964.6488405</v>
+        <v>-4008.94216095</v>
       </c>
       <c r="Q92">
-        <v>-3963.8488405</v>
+        <v>-4008.14216095</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.70027610846877</v>
+        <v>0.772995676076411</v>
       </c>
       <c r="T92">
-        <v>9.523424833104947</v>
+        <v>10.58158314789438</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.001364013039728356</v>
+        <v>0.001349023885445627</v>
       </c>
       <c r="W92">
-        <v>0.2354783657252321</v>
+        <v>0.2354819001678119</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.005456052158913427</v>
+        <v>0.005396095541782553</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2838581399995858</v>
+        <v>0.2857581399995859</v>
       </c>
       <c r="C93">
-        <v>-15889.23686152931</v>
+        <v>-16194.21793503278</v>
       </c>
       <c r="D93">
-        <v>6886.050138470696</v>
+        <v>6831.52606496722</v>
       </c>
       <c r="E93">
-        <v>22699.287</v>
+        <v>22949.744</v>
       </c>
       <c r="F93">
-        <v>22791.587</v>
+        <v>23042.044</v>
       </c>
       <c r="G93">
         <v>16.3</v>
@@ -8907,37 +8907,37 @@
         <v>29</v>
       </c>
       <c r="M93">
-        <v>5374.256214600001</v>
+        <v>5433.313975200001</v>
       </c>
       <c r="N93">
-        <v>-5345.256214600001</v>
+        <v>-5404.313975200001</v>
       </c>
       <c r="O93">
-        <v>-1336.31405365</v>
+        <v>-1351.0784938</v>
       </c>
       <c r="P93">
-        <v>-4008.94216095</v>
+        <v>-4053.2354814</v>
       </c>
       <c r="Q93">
-        <v>-4008.14216095</v>
+        <v>-4052.4354814</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.772995676076411</v>
+        <v>0.8638951355859626</v>
       </c>
       <c r="T93">
-        <v>10.58158314789438</v>
+        <v>11.90428104138119</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.001349023885445627</v>
+        <v>0.001334360582342957</v>
       </c>
       <c r="W93">
-        <v>0.2354819001678119</v>
+        <v>0.2354853577746835</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.005396095541782553</v>
+        <v>0.005337442329371833</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2857581399995859</v>
+        <v>0.2876581399995858</v>
       </c>
       <c r="C94">
-        <v>-16194.21793503278</v>
+        <v>-16498.3423432228</v>
       </c>
       <c r="D94">
-        <v>6831.52606496722</v>
+        <v>6777.858656777196</v>
       </c>
       <c r="E94">
-        <v>22949.744</v>
+        <v>23200.201</v>
       </c>
       <c r="F94">
-        <v>23042.044</v>
+        <v>23292.501</v>
       </c>
       <c r="G94">
         <v>16.3</v>
@@ -8989,37 +8989,37 @@
         <v>29</v>
       </c>
       <c r="M94">
-        <v>5433.313975200001</v>
+        <v>5492.3717358</v>
       </c>
       <c r="N94">
-        <v>-5404.313975200001</v>
+        <v>-5463.3717358</v>
       </c>
       <c r="O94">
-        <v>-1351.0784938</v>
+        <v>-1365.84293395</v>
       </c>
       <c r="P94">
-        <v>-4053.2354814</v>
+        <v>-4097.52880185</v>
       </c>
       <c r="Q94">
-        <v>-4052.4354814</v>
+        <v>-4096.72880185</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8638951355859626</v>
+        <v>0.9807658692411004</v>
       </c>
       <c r="T94">
-        <v>11.90428104138119</v>
+        <v>13.60489261872136</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.001334360582342957</v>
+        <v>0.001320012619091958</v>
       </c>
       <c r="W94">
-        <v>0.2354853577746835</v>
+        <v>0.2354887410244181</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.005337442329371833</v>
+        <v>0.005280050476367815</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2876581399995858</v>
+        <v>0.2895581399995859</v>
       </c>
       <c r="C95">
-        <v>-16498.3423432228</v>
+        <v>-16801.63011821928</v>
       </c>
       <c r="D95">
-        <v>6777.858656777196</v>
+        <v>6725.027881780721</v>
       </c>
       <c r="E95">
-        <v>23200.201</v>
+        <v>23450.658</v>
       </c>
       <c r="F95">
-        <v>23292.501</v>
+        <v>23542.958</v>
       </c>
       <c r="G95">
         <v>16.3</v>
@@ -9071,37 +9071,37 @@
         <v>29</v>
       </c>
       <c r="M95">
-        <v>5492.3717358</v>
+        <v>5551.429496400001</v>
       </c>
       <c r="N95">
-        <v>-5463.3717358</v>
+        <v>-5522.429496400001</v>
       </c>
       <c r="O95">
-        <v>-1365.84293395</v>
+        <v>-1380.6073741</v>
       </c>
       <c r="P95">
-        <v>-4097.52880185</v>
+        <v>-4141.822122300001</v>
       </c>
       <c r="Q95">
-        <v>-4096.72880185</v>
+        <v>-4141.022122300001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9807658692411004</v>
+        <v>1.136593514114617</v>
       </c>
       <c r="T95">
-        <v>13.60489261872136</v>
+        <v>15.87237472184159</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.001320012619091958</v>
+        <v>0.001305969931654809</v>
       </c>
       <c r="W95">
-        <v>0.2354887410244181</v>
+        <v>0.2354920522901158</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.005280050476367815</v>
+        <v>0.005223879726619196</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2895581399995859</v>
+        <v>0.2914581399995859</v>
       </c>
       <c r="C96">
-        <v>-16801.63011821928</v>
+        <v>-17104.10067240236</v>
       </c>
       <c r="D96">
-        <v>6725.027881780721</v>
+        <v>6673.014327597642</v>
       </c>
       <c r="E96">
-        <v>23450.658</v>
+        <v>23701.115</v>
       </c>
       <c r="F96">
-        <v>23542.958</v>
+        <v>23793.415</v>
       </c>
       <c r="G96">
         <v>16.3</v>
@@ -9153,37 +9153,37 @@
         <v>29</v>
       </c>
       <c r="M96">
-        <v>5551.429496400001</v>
+        <v>5610.487257000001</v>
       </c>
       <c r="N96">
-        <v>-5522.429496400001</v>
+        <v>-5581.487257000001</v>
       </c>
       <c r="O96">
-        <v>-1380.6073741</v>
+        <v>-1395.37181425</v>
       </c>
       <c r="P96">
-        <v>-4141.822122300001</v>
+        <v>-4186.115442750001</v>
       </c>
       <c r="Q96">
-        <v>-4141.022122300001</v>
+        <v>-4185.31544275</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.136593514114617</v>
+        <v>1.354752216937542</v>
       </c>
       <c r="T96">
-        <v>15.87237472184159</v>
+        <v>19.04684966620992</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.001305969931654809</v>
+        <v>0.001292222879742653</v>
       </c>
       <c r="W96">
-        <v>0.2354920522901158</v>
+        <v>0.2354952938449567</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.005223879726619196</v>
+        <v>0.005168891518970598</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2914581399995859</v>
+        <v>0.2933581399995858</v>
       </c>
       <c r="C97">
-        <v>-17104.10067240236</v>
+        <v>-17405.77282219488</v>
       </c>
       <c r="D97">
-        <v>6673.014327597642</v>
+        <v>6621.799177805126</v>
       </c>
       <c r="E97">
-        <v>23701.115</v>
+        <v>23951.572</v>
       </c>
       <c r="F97">
-        <v>23793.415</v>
+        <v>24043.872</v>
       </c>
       <c r="G97">
         <v>16.3</v>
@@ -9235,37 +9235,37 @@
         <v>29</v>
       </c>
       <c r="M97">
-        <v>5610.487257000001</v>
+        <v>5669.545017600001</v>
       </c>
       <c r="N97">
-        <v>-5581.487257000001</v>
+        <v>-5640.545017600001</v>
       </c>
       <c r="O97">
-        <v>-1395.37181425</v>
+        <v>-1410.1362544</v>
       </c>
       <c r="P97">
-        <v>-4186.115442750001</v>
+        <v>-4230.408763200001</v>
       </c>
       <c r="Q97">
-        <v>-4185.31544275</v>
+        <v>-4229.608763200001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.354752216937542</v>
+        <v>1.681990271171928</v>
       </c>
       <c r="T97">
-        <v>19.04684966620992</v>
+        <v>23.80856208276241</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.001292222879742653</v>
+        <v>0.001278762224745334</v>
       </c>
       <c r="W97">
-        <v>0.2354952938449567</v>
+        <v>0.2354984678674051</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.005168891518970598</v>
+        <v>0.005115048898981289</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2933581399995858</v>
+        <v>0.2952581399995858</v>
       </c>
       <c r="C98">
-        <v>-17405.77282219487</v>
+        <v>-17706.66481075789</v>
       </c>
       <c r="D98">
-        <v>6621.799177805126</v>
+        <v>6571.364189242115</v>
       </c>
       <c r="E98">
-        <v>23951.572</v>
+        <v>24202.029</v>
       </c>
       <c r="F98">
-        <v>24043.872</v>
+        <v>24294.329</v>
       </c>
       <c r="G98">
         <v>16.3</v>
@@ -9317,37 +9317,37 @@
         <v>29</v>
       </c>
       <c r="M98">
-        <v>5669.5450176</v>
+        <v>5728.602778200001</v>
       </c>
       <c r="N98">
-        <v>-5640.5450176</v>
+        <v>-5699.602778200001</v>
       </c>
       <c r="O98">
-        <v>-1410.1362544</v>
+        <v>-1424.90069455</v>
       </c>
       <c r="P98">
-        <v>-4230.4087632</v>
+        <v>-4274.702083650001</v>
       </c>
       <c r="Q98">
-        <v>-4229.6087632</v>
+        <v>-4273.90208365</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.681990271171923</v>
+        <v>2.227387028229231</v>
       </c>
       <c r="T98">
-        <v>23.80856208276234</v>
+        <v>31.74474944368312</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.001278762224745334</v>
+        <v>0.00126557910902631</v>
       </c>
       <c r="W98">
-        <v>0.2354984678674051</v>
+        <v>0.2355015764460916</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.005115048898981289</v>
+        <v>0.005062316436105219</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2952581399995858</v>
+        <v>0.2971581399995858</v>
       </c>
       <c r="C99">
-        <v>-17706.66481075789</v>
+        <v>-18006.79432965694</v>
       </c>
       <c r="D99">
-        <v>6571.364189242115</v>
+        <v>6521.691670343062</v>
       </c>
       <c r="E99">
-        <v>24202.029</v>
+        <v>24452.486</v>
       </c>
       <c r="F99">
-        <v>24294.329</v>
+        <v>24544.786</v>
       </c>
       <c r="G99">
         <v>16.3</v>
@@ -9399,37 +9399,37 @@
         <v>29</v>
       </c>
       <c r="M99">
-        <v>5728.602778200001</v>
+        <v>5787.6605388</v>
       </c>
       <c r="N99">
-        <v>-5699.602778200001</v>
+        <v>-5758.6605388</v>
       </c>
       <c r="O99">
-        <v>-1424.90069455</v>
+        <v>-1439.6651347</v>
       </c>
       <c r="P99">
-        <v>-4274.702083650001</v>
+        <v>-4318.9954041</v>
       </c>
       <c r="Q99">
-        <v>-4273.90208365</v>
+        <v>-4318.1954041</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.227387028229231</v>
+        <v>3.318180542343846</v>
       </c>
       <c r="T99">
-        <v>31.74474944368312</v>
+        <v>47.61712416552469</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.00126557910902631</v>
+        <v>0.001252665036485225</v>
       </c>
       <c r="W99">
-        <v>0.2355015764460916</v>
+        <v>0.2355046215843968</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.005062316436105219</v>
+        <v>0.005010660145940871</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2971581399995858</v>
+        <v>0.2990581399995859</v>
       </c>
       <c r="C100">
-        <v>-18006.79432965694</v>
+        <v>-18306.17853955302</v>
       </c>
       <c r="D100">
-        <v>6521.691670343062</v>
+        <v>6472.764460446977</v>
       </c>
       <c r="E100">
-        <v>24452.486</v>
+        <v>24702.943</v>
       </c>
       <c r="F100">
-        <v>24544.786</v>
+        <v>24795.243</v>
       </c>
       <c r="G100">
         <v>16.3</v>
@@ -9481,37 +9481,37 @@
         <v>29</v>
       </c>
       <c r="M100">
-        <v>5787.6605388</v>
+        <v>5846.7182994</v>
       </c>
       <c r="N100">
-        <v>-5758.6605388</v>
+        <v>-5817.7182994</v>
       </c>
       <c r="O100">
-        <v>-1439.6651347</v>
+        <v>-1454.42957485</v>
       </c>
       <c r="P100">
-        <v>-4318.9954041</v>
+        <v>-4363.288724550001</v>
       </c>
       <c r="Q100">
-        <v>-4318.1954041</v>
+        <v>-4362.48872455</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.318180542343846</v>
+        <v>6.590561084687693</v>
       </c>
       <c r="T100">
-        <v>47.61712416552469</v>
+        <v>95.23424833104937</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.001252665036485225</v>
+        <v>0.001240011854298506</v>
       </c>
       <c r="W100">
-        <v>0.2355046215843968</v>
+        <v>0.2355076052047564</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.005010660145940871</v>
+        <v>0.004960047417194025</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2990581399995859</v>
-      </c>
-      <c r="C101">
-        <v>-18306.17853955302</v>
-      </c>
-      <c r="D101">
-        <v>6472.764460446977</v>
-      </c>
-      <c r="E101">
-        <v>24702.943</v>
-      </c>
-      <c r="F101">
-        <v>24795.243</v>
-      </c>
-      <c r="G101">
-        <v>16.3</v>
-      </c>
-      <c r="H101">
-        <v>24953.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>29.8</v>
-      </c>
-      <c r="K101">
-        <v>0.8000000000000007</v>
-      </c>
-      <c r="L101">
-        <v>29</v>
-      </c>
-      <c r="M101">
-        <v>5846.7182994</v>
-      </c>
-      <c r="N101">
-        <v>-5817.7182994</v>
-      </c>
-      <c r="O101">
-        <v>-1454.42957485</v>
-      </c>
-      <c r="P101">
-        <v>-4363.288724550001</v>
-      </c>
-      <c r="Q101">
-        <v>-4362.48872455</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.590561084687693</v>
-      </c>
-      <c r="T101">
-        <v>95.23424833104937</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.001240011854298506</v>
-      </c>
-      <c r="W101">
-        <v>0.2355076052047564</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.004960047417194025</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
